--- a/inst/extdata/moxy_ramp.xlsx
+++ b/inst/extdata/moxy_ramp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R-Projects\mnirs\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EBA7D6-2E4B-4221-840C-8DD290E8AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CC3548-0C30-4ABC-8757-59C29C3D17A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="31785" xr2:uid="{ED07EABD-9B2D-42C5-B904-3B14C8E7B28A}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="2209">
-  <si>
-    <t>0:29:00.01</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="2208">
   <si>
     <t>0:29:00.41</t>
   </si>
@@ -7524,7 +7521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B18608-BA4B-422A-BDE0-919FC8A5223C}">
-  <dimension ref="A1:E2392"/>
+  <dimension ref="A1:E2391"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -7534,39 +7531,39 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B6" t="s">
         <v>2201</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>2202</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E6" t="s">
         <v>2203</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2207</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7614,7 +7611,7 @@
         <v>54</v>
       </c>
       <c r="D9">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7679,10 +7676,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -7747,10 +7744,10 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D17">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -7798,10 +7795,10 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -7866,10 +7863,10 @@
         <v>17</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -7934,10 +7931,10 @@
         <v>21</v>
       </c>
       <c r="C28">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -7985,10 +7982,10 @@
         <v>24</v>
       </c>
       <c r="C31">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -8053,10 +8050,10 @@
         <v>28</v>
       </c>
       <c r="C35">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -8104,10 +8101,10 @@
         <v>31</v>
       </c>
       <c r="C38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D38">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -8172,10 +8169,10 @@
         <v>35</v>
       </c>
       <c r="C42">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -8240,7 +8237,7 @@
         <v>39</v>
       </c>
       <c r="C46">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D46">
         <v>66</v>
@@ -8291,10 +8288,10 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D49">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -8481,7 +8478,7 @@
         <v>56</v>
       </c>
       <c r="D60">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -8546,10 +8543,10 @@
         <v>57</v>
       </c>
       <c r="C64">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -8597,10 +8594,10 @@
         <v>60</v>
       </c>
       <c r="C67">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -8665,10 +8662,10 @@
         <v>64</v>
       </c>
       <c r="C71">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D71">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -8736,7 +8733,7 @@
         <v>56</v>
       </c>
       <c r="D75">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -8787,7 +8784,7 @@
         <v>56</v>
       </c>
       <c r="D78">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -8852,10 +8849,10 @@
         <v>75</v>
       </c>
       <c r="C82">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D82">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -8923,7 +8920,7 @@
         <v>55</v>
       </c>
       <c r="D86">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -8937,7 +8934,7 @@
         <v>80</v>
       </c>
       <c r="C87">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D87">
         <v>63</v>
@@ -8971,10 +8968,10 @@
         <v>82</v>
       </c>
       <c r="C89">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D89">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -9042,7 +9039,7 @@
         <v>55</v>
       </c>
       <c r="D93">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -9110,7 +9107,7 @@
         <v>55</v>
       </c>
       <c r="D97">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -9158,10 +9155,10 @@
         <v>93</v>
       </c>
       <c r="C100">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D100">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -9226,10 +9223,10 @@
         <v>97</v>
       </c>
       <c r="C104">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D104">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -9277,10 +9274,10 @@
         <v>100</v>
       </c>
       <c r="C107">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D107">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -9348,7 +9345,7 @@
         <v>56</v>
       </c>
       <c r="D111">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -9413,10 +9410,10 @@
         <v>108</v>
       </c>
       <c r="C115">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D115">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -9463,11 +9460,8 @@
       <c r="B118" t="s">
         <v>111</v>
       </c>
-      <c r="C118">
-        <v>55</v>
-      </c>
       <c r="D118">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -9523,7 +9517,7 @@
         <v>115</v>
       </c>
       <c r="D122">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -9579,7 +9573,7 @@
         <v>119</v>
       </c>
       <c r="D126">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -9621,7 +9615,7 @@
         <v>122</v>
       </c>
       <c r="D129">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -9677,7 +9671,7 @@
         <v>126</v>
       </c>
       <c r="D133">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -9719,7 +9713,7 @@
         <v>129</v>
       </c>
       <c r="D136">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -9775,7 +9769,7 @@
         <v>133</v>
       </c>
       <c r="D140">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -9831,7 +9825,7 @@
         <v>137</v>
       </c>
       <c r="D144">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -9929,7 +9923,7 @@
         <v>144</v>
       </c>
       <c r="D151">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -9985,7 +9979,7 @@
         <v>148</v>
       </c>
       <c r="D155">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -10027,7 +10021,7 @@
         <v>151</v>
       </c>
       <c r="D158">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E158">
         <v>1</v>
@@ -10083,7 +10077,7 @@
         <v>155</v>
       </c>
       <c r="D162">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -10110,6 +10104,9 @@
       <c r="B164" t="s">
         <v>157</v>
       </c>
+      <c r="C164">
+        <v>57</v>
+      </c>
       <c r="D164">
         <v>67</v>
       </c>
@@ -10196,7 +10193,7 @@
         <v>57</v>
       </c>
       <c r="D169">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -10244,7 +10241,7 @@
         <v>165</v>
       </c>
       <c r="C172">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D172">
         <v>68</v>
@@ -10295,7 +10292,7 @@
         <v>168</v>
       </c>
       <c r="C175">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D175">
         <v>68</v>
@@ -10315,7 +10312,7 @@
         <v>58</v>
       </c>
       <c r="D176">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -10363,7 +10360,7 @@
         <v>172</v>
       </c>
       <c r="C179">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D179">
         <v>67</v>
@@ -10383,7 +10380,7 @@
         <v>55</v>
       </c>
       <c r="D180">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -10414,7 +10411,7 @@
         <v>175</v>
       </c>
       <c r="C182">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D182">
         <v>70</v>
@@ -10502,7 +10499,7 @@
         <v>57</v>
       </c>
       <c r="D187">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -10567,10 +10564,10 @@
         <v>184</v>
       </c>
       <c r="C191">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D191">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -10601,7 +10598,7 @@
         <v>186</v>
       </c>
       <c r="C193">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D193">
         <v>66</v>
@@ -10638,7 +10635,7 @@
         <v>57</v>
       </c>
       <c r="D195">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -10669,7 +10666,7 @@
         <v>190</v>
       </c>
       <c r="C197">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D197">
         <v>68</v>
@@ -10689,7 +10686,7 @@
         <v>55</v>
       </c>
       <c r="D198">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -10737,7 +10734,7 @@
         <v>194</v>
       </c>
       <c r="C201">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D201">
         <v>67</v>
@@ -10757,7 +10754,7 @@
         <v>54</v>
       </c>
       <c r="D202">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -10788,7 +10785,7 @@
         <v>197</v>
       </c>
       <c r="C204">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D204">
         <v>64</v>
@@ -10808,7 +10805,7 @@
         <v>57</v>
       </c>
       <c r="D205">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -10856,7 +10853,7 @@
         <v>201</v>
       </c>
       <c r="C208">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D208">
         <v>65</v>
@@ -10876,7 +10873,7 @@
         <v>55</v>
       </c>
       <c r="D209">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -10975,7 +10972,7 @@
         <v>208</v>
       </c>
       <c r="C215">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D215">
         <v>67</v>
@@ -10995,7 +10992,7 @@
         <v>56</v>
       </c>
       <c r="D216">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -11043,7 +11040,7 @@
         <v>212</v>
       </c>
       <c r="C219">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D219">
         <v>66</v>
@@ -11094,7 +11091,7 @@
         <v>215</v>
       </c>
       <c r="C222">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D222">
         <v>66</v>
@@ -11131,7 +11128,7 @@
         <v>57</v>
       </c>
       <c r="D224">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -11199,7 +11196,7 @@
         <v>57</v>
       </c>
       <c r="D228">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -11230,7 +11227,7 @@
         <v>223</v>
       </c>
       <c r="C230">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D230">
         <v>63</v>
@@ -11250,7 +11247,7 @@
         <v>56</v>
       </c>
       <c r="D231">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -11281,7 +11278,7 @@
         <v>226</v>
       </c>
       <c r="C233">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D233">
         <v>59</v>
@@ -11318,7 +11315,7 @@
         <v>54</v>
       </c>
       <c r="D235">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -11369,7 +11366,7 @@
         <v>54</v>
       </c>
       <c r="D238">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -11437,7 +11434,7 @@
         <v>54</v>
       </c>
       <c r="D242">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -11468,7 +11465,7 @@
         <v>237</v>
       </c>
       <c r="C244">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D244">
         <v>64</v>
@@ -11488,7 +11485,7 @@
         <v>53</v>
       </c>
       <c r="D245">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -11536,7 +11533,7 @@
         <v>241</v>
       </c>
       <c r="C248">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D248">
         <v>61</v>
@@ -11556,7 +11553,7 @@
         <v>52</v>
       </c>
       <c r="D249">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E249">
         <v>1</v>
@@ -11587,7 +11584,7 @@
         <v>244</v>
       </c>
       <c r="C251">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D251">
         <v>60</v>
@@ -11624,7 +11621,7 @@
         <v>53</v>
       </c>
       <c r="D253">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -11655,7 +11652,7 @@
         <v>248</v>
       </c>
       <c r="C255">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D255">
         <v>64</v>
@@ -11743,7 +11740,7 @@
         <v>55</v>
       </c>
       <c r="D260">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -11774,7 +11771,7 @@
         <v>255</v>
       </c>
       <c r="C262">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D262">
         <v>60</v>
@@ -11811,7 +11808,7 @@
         <v>57</v>
       </c>
       <c r="D264">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E264">
         <v>1</v>
@@ -11842,7 +11839,7 @@
         <v>259</v>
       </c>
       <c r="C266">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D266">
         <v>63</v>
@@ -11862,7 +11859,7 @@
         <v>56</v>
       </c>
       <c r="D267">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -11930,7 +11927,7 @@
         <v>56</v>
       </c>
       <c r="D271">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E271">
         <v>1</v>
@@ -11981,7 +11978,7 @@
         <v>56</v>
       </c>
       <c r="D274">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E274">
         <v>1</v>
@@ -12029,7 +12026,7 @@
         <v>270</v>
       </c>
       <c r="C277">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D277">
         <v>56</v>
@@ -12049,7 +12046,7 @@
         <v>53</v>
       </c>
       <c r="D278">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -12097,7 +12094,7 @@
         <v>274</v>
       </c>
       <c r="C281">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D281">
         <v>55</v>
@@ -12117,7 +12114,7 @@
         <v>57</v>
       </c>
       <c r="D282">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E282">
         <v>1</v>
@@ -12148,7 +12145,7 @@
         <v>277</v>
       </c>
       <c r="C284">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D284">
         <v>57</v>
@@ -12168,7 +12165,7 @@
         <v>58</v>
       </c>
       <c r="D285">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E285">
         <v>1</v>
@@ -12216,7 +12213,7 @@
         <v>281</v>
       </c>
       <c r="C288">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D288">
         <v>52</v>
@@ -12236,7 +12233,7 @@
         <v>48</v>
       </c>
       <c r="D289">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E289">
         <v>1</v>
@@ -12284,7 +12281,7 @@
         <v>285</v>
       </c>
       <c r="C292">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D292">
         <v>50</v>
@@ -12304,7 +12301,7 @@
         <v>47</v>
       </c>
       <c r="D293">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E293">
         <v>1</v>
@@ -12335,7 +12332,7 @@
         <v>288</v>
       </c>
       <c r="C295">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D295">
         <v>52</v>
@@ -12355,7 +12352,7 @@
         <v>52</v>
       </c>
       <c r="D296">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E296">
         <v>1</v>
@@ -12403,7 +12400,7 @@
         <v>292</v>
       </c>
       <c r="C299">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D299">
         <v>56</v>
@@ -12423,7 +12420,7 @@
         <v>49</v>
       </c>
       <c r="D300">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E300">
         <v>1</v>
@@ -12454,7 +12451,7 @@
         <v>295</v>
       </c>
       <c r="C302">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D302">
         <v>62</v>
@@ -12491,7 +12488,7 @@
         <v>45</v>
       </c>
       <c r="D304">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E304">
         <v>1</v>
@@ -12522,7 +12519,7 @@
         <v>299</v>
       </c>
       <c r="C306">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D306">
         <v>64</v>
@@ -12542,7 +12539,7 @@
         <v>51</v>
       </c>
       <c r="D307">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E307">
         <v>1</v>
@@ -12590,7 +12587,7 @@
         <v>303</v>
       </c>
       <c r="C310">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D310">
         <v>65</v>
@@ -12610,7 +12607,7 @@
         <v>56</v>
       </c>
       <c r="D311">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E311">
         <v>1</v>
@@ -12641,7 +12638,7 @@
         <v>306</v>
       </c>
       <c r="C313">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D313">
         <v>58</v>
@@ -12661,7 +12658,7 @@
         <v>53</v>
       </c>
       <c r="D314">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E314">
         <v>1</v>
@@ -12709,7 +12706,7 @@
         <v>310</v>
       </c>
       <c r="C317">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D317">
         <v>56</v>
@@ -12729,7 +12726,7 @@
         <v>50</v>
       </c>
       <c r="D318">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E318">
         <v>1</v>
@@ -12828,7 +12825,7 @@
         <v>317</v>
       </c>
       <c r="C324">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D324">
         <v>59</v>
@@ -12848,7 +12845,7 @@
         <v>51</v>
       </c>
       <c r="D325">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E325">
         <v>1</v>
@@ -12896,7 +12893,7 @@
         <v>321</v>
       </c>
       <c r="C328">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D328">
         <v>56</v>
@@ -12916,7 +12913,7 @@
         <v>52</v>
       </c>
       <c r="D329">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -12984,7 +12981,7 @@
         <v>52</v>
       </c>
       <c r="D333">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E333">
         <v>1</v>
@@ -13015,7 +13012,7 @@
         <v>328</v>
       </c>
       <c r="C335">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D335">
         <v>62</v>
@@ -13066,7 +13063,7 @@
         <v>331</v>
       </c>
       <c r="C338">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D338">
         <v>62</v>
@@ -13103,7 +13100,7 @@
         <v>49</v>
       </c>
       <c r="D340">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E340">
         <v>1</v>
@@ -13134,7 +13131,7 @@
         <v>335</v>
       </c>
       <c r="C342">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D342">
         <v>61</v>
@@ -13154,7 +13151,7 @@
         <v>54</v>
       </c>
       <c r="D343">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E343">
         <v>1</v>
@@ -13202,7 +13199,7 @@
         <v>339</v>
       </c>
       <c r="C346">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D346">
         <v>64</v>
@@ -13253,7 +13250,7 @@
         <v>342</v>
       </c>
       <c r="C349">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D349">
         <v>64</v>
@@ -13290,7 +13287,7 @@
         <v>51</v>
       </c>
       <c r="D351">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E351">
         <v>1</v>
@@ -13321,7 +13318,7 @@
         <v>346</v>
       </c>
       <c r="C353">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D353">
         <v>59</v>
@@ -13372,7 +13369,7 @@
         <v>349</v>
       </c>
       <c r="C356">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D356">
         <v>59</v>
@@ -13409,7 +13406,7 @@
         <v>55</v>
       </c>
       <c r="D358">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E358">
         <v>1</v>
@@ -13440,7 +13437,7 @@
         <v>353</v>
       </c>
       <c r="C360">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D360">
         <v>65</v>
@@ -13477,7 +13474,7 @@
         <v>54</v>
       </c>
       <c r="D362">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E362">
         <v>1</v>
@@ -13508,7 +13505,7 @@
         <v>357</v>
       </c>
       <c r="C364">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D364">
         <v>67</v>
@@ -13528,7 +13525,7 @@
         <v>51</v>
       </c>
       <c r="D365">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E365">
         <v>1</v>
@@ -13559,7 +13556,7 @@
         <v>360</v>
       </c>
       <c r="C367">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D367">
         <v>64</v>
@@ -13596,7 +13593,7 @@
         <v>54</v>
       </c>
       <c r="D369">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E369">
         <v>1</v>
@@ -13627,7 +13624,7 @@
         <v>364</v>
       </c>
       <c r="C371">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D371">
         <v>67</v>
@@ -13695,7 +13692,7 @@
         <v>368</v>
       </c>
       <c r="C375">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D375">
         <v>67</v>
@@ -13715,10 +13712,10 @@
         <v>50</v>
       </c>
       <c r="D376">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E376">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -13746,7 +13743,7 @@
         <v>371</v>
       </c>
       <c r="C378">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D378">
         <v>66</v>
@@ -13783,7 +13780,7 @@
         <v>44</v>
       </c>
       <c r="D380">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E380">
         <v>2</v>
@@ -13814,7 +13811,7 @@
         <v>375</v>
       </c>
       <c r="C382">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D382">
         <v>60</v>
@@ -13851,7 +13848,7 @@
         <v>47</v>
       </c>
       <c r="D384">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E384">
         <v>2</v>
@@ -13882,7 +13879,7 @@
         <v>379</v>
       </c>
       <c r="C386">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D386">
         <v>58</v>
@@ -13933,7 +13930,7 @@
         <v>382</v>
       </c>
       <c r="C389">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D389">
         <v>58</v>
@@ -13970,7 +13967,7 @@
         <v>57</v>
       </c>
       <c r="D391">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E391">
         <v>2</v>
@@ -13998,10 +13995,10 @@
         <v>45694</v>
       </c>
       <c r="B393" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C393">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D393">
         <v>63</v>
@@ -14015,7 +14012,7 @@
         <v>45694</v>
       </c>
       <c r="B394" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C394">
         <v>53</v>
@@ -14072,7 +14069,7 @@
         <v>53</v>
       </c>
       <c r="D397">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E397">
         <v>2</v>
@@ -14103,7 +14100,7 @@
         <v>390</v>
       </c>
       <c r="C399">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D399">
         <v>62</v>
@@ -14140,7 +14137,7 @@
         <v>52</v>
       </c>
       <c r="D401">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E401">
         <v>2</v>
@@ -14171,7 +14168,7 @@
         <v>394</v>
       </c>
       <c r="C403">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D403">
         <v>64</v>
@@ -14208,7 +14205,7 @@
         <v>57</v>
       </c>
       <c r="D405">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E405">
         <v>2</v>
@@ -14239,7 +14236,7 @@
         <v>398</v>
       </c>
       <c r="C407">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D407">
         <v>66</v>
@@ -14259,7 +14256,7 @@
         <v>56</v>
       </c>
       <c r="D408">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E408">
         <v>2</v>
@@ -14290,7 +14287,7 @@
         <v>401</v>
       </c>
       <c r="C410">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D410">
         <v>63</v>
@@ -14327,7 +14324,7 @@
         <v>50</v>
       </c>
       <c r="D412">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E412">
         <v>2</v>
@@ -14358,7 +14355,7 @@
         <v>405</v>
       </c>
       <c r="C414">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D414">
         <v>64</v>
@@ -14395,7 +14392,7 @@
         <v>53</v>
       </c>
       <c r="D416">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E416">
         <v>2</v>
@@ -14446,7 +14443,7 @@
         <v>53</v>
       </c>
       <c r="D419">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E419">
         <v>2</v>
@@ -14477,7 +14474,7 @@
         <v>412</v>
       </c>
       <c r="C421">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D421">
         <v>63</v>
@@ -14514,7 +14511,7 @@
         <v>48</v>
       </c>
       <c r="D423">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E423">
         <v>2</v>
@@ -14545,7 +14542,7 @@
         <v>416</v>
       </c>
       <c r="C425">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D425">
         <v>62</v>
@@ -14565,7 +14562,7 @@
         <v>50</v>
       </c>
       <c r="D426">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E426">
         <v>2</v>
@@ -14596,7 +14593,7 @@
         <v>419</v>
       </c>
       <c r="C428">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D428">
         <v>64</v>
@@ -14664,7 +14661,7 @@
         <v>423</v>
       </c>
       <c r="C432">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D432">
         <v>64</v>
@@ -14701,7 +14698,7 @@
         <v>53</v>
       </c>
       <c r="D434">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E434">
         <v>2</v>
@@ -14732,7 +14729,7 @@
         <v>427</v>
       </c>
       <c r="C436">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D436">
         <v>61</v>
@@ -14752,7 +14749,7 @@
         <v>49</v>
       </c>
       <c r="D437">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E437">
         <v>2</v>
@@ -14783,7 +14780,7 @@
         <v>430</v>
       </c>
       <c r="C439">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D439">
         <v>60</v>
@@ -14820,7 +14817,7 @@
         <v>50</v>
       </c>
       <c r="D441">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E441">
         <v>2</v>
@@ -14851,7 +14848,7 @@
         <v>434</v>
       </c>
       <c r="C443">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D443">
         <v>66</v>
@@ -14888,7 +14885,7 @@
         <v>54</v>
       </c>
       <c r="D445">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E445">
         <v>2</v>
@@ -14919,7 +14916,7 @@
         <v>438</v>
       </c>
       <c r="C447">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D447">
         <v>65</v>
@@ -14939,7 +14936,7 @@
         <v>51</v>
       </c>
       <c r="D448">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E448">
         <v>2</v>
@@ -14970,7 +14967,7 @@
         <v>441</v>
       </c>
       <c r="C450">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D450">
         <v>60</v>
@@ -15038,7 +15035,7 @@
         <v>445</v>
       </c>
       <c r="C454">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D454">
         <v>60</v>
@@ -15058,7 +15055,7 @@
         <v>52</v>
       </c>
       <c r="D455">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E455">
         <v>2</v>
@@ -15089,7 +15086,7 @@
         <v>448</v>
       </c>
       <c r="C457">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D457">
         <v>65</v>
@@ -15126,7 +15123,7 @@
         <v>54</v>
       </c>
       <c r="D459">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E459">
         <v>2</v>
@@ -15157,7 +15154,7 @@
         <v>452</v>
       </c>
       <c r="C461">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D461">
         <v>63</v>
@@ -15194,7 +15191,7 @@
         <v>48</v>
       </c>
       <c r="D463">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E463">
         <v>2</v>
@@ -15245,7 +15242,7 @@
         <v>48</v>
       </c>
       <c r="D466">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E466">
         <v>2</v>
@@ -15276,7 +15273,7 @@
         <v>459</v>
       </c>
       <c r="C468">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D468">
         <v>61</v>
@@ -15313,7 +15310,7 @@
         <v>50</v>
       </c>
       <c r="D470">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E470">
         <v>2</v>
@@ -15344,7 +15341,7 @@
         <v>463</v>
       </c>
       <c r="C472">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D472">
         <v>65</v>
@@ -15381,7 +15378,7 @@
         <v>52</v>
       </c>
       <c r="D474">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E474">
         <v>2</v>
@@ -15412,7 +15409,7 @@
         <v>467</v>
       </c>
       <c r="C476">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D476">
         <v>62</v>
@@ -15432,7 +15429,7 @@
         <v>47</v>
       </c>
       <c r="D477">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E477">
         <v>2</v>
@@ -15500,7 +15497,7 @@
         <v>47</v>
       </c>
       <c r="D481">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E481">
         <v>2</v>
@@ -15531,7 +15528,7 @@
         <v>474</v>
       </c>
       <c r="C483">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D483">
         <v>62</v>
@@ -15568,7 +15565,7 @@
         <v>51</v>
       </c>
       <c r="D485">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E485">
         <v>2</v>
@@ -15599,7 +15596,7 @@
         <v>478</v>
       </c>
       <c r="C487">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D487">
         <v>64</v>
@@ -15619,7 +15616,7 @@
         <v>52</v>
       </c>
       <c r="D488">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E488">
         <v>2</v>
@@ -15650,7 +15647,7 @@
         <v>481</v>
       </c>
       <c r="C490">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D490">
         <v>62</v>
@@ -15687,7 +15684,7 @@
         <v>46</v>
       </c>
       <c r="D492">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E492">
         <v>2</v>
@@ -15718,7 +15715,7 @@
         <v>485</v>
       </c>
       <c r="C494">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D494">
         <v>56</v>
@@ -15738,7 +15735,7 @@
         <v>47</v>
       </c>
       <c r="D495">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E495">
         <v>2</v>
@@ -15769,7 +15766,7 @@
         <v>488</v>
       </c>
       <c r="C497">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D497">
         <v>60</v>
@@ -15806,7 +15803,7 @@
         <v>50</v>
       </c>
       <c r="D499">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E499">
         <v>2</v>
@@ -15837,7 +15834,7 @@
         <v>492</v>
       </c>
       <c r="C501">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D501">
         <v>61</v>
@@ -15905,7 +15902,7 @@
         <v>496</v>
       </c>
       <c r="C505">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D505">
         <v>61</v>
@@ -15925,7 +15922,7 @@
         <v>46</v>
       </c>
       <c r="D506">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E506">
         <v>2</v>
@@ -15956,7 +15953,7 @@
         <v>499</v>
       </c>
       <c r="C508">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D508">
         <v>58</v>
@@ -15993,7 +15990,7 @@
         <v>45</v>
       </c>
       <c r="D510">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E510">
         <v>2</v>
@@ -16024,7 +16021,7 @@
         <v>503</v>
       </c>
       <c r="C512">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D512">
         <v>57</v>
@@ -16061,7 +16058,7 @@
         <v>48</v>
       </c>
       <c r="D514">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E514">
         <v>2</v>
@@ -16092,7 +16089,7 @@
         <v>507</v>
       </c>
       <c r="C516">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D516">
         <v>59</v>
@@ -16129,7 +16126,7 @@
         <v>49</v>
       </c>
       <c r="D518">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E518">
         <v>2</v>
@@ -16143,7 +16140,7 @@
         <v>510</v>
       </c>
       <c r="C519">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D519">
         <v>60</v>
@@ -16180,7 +16177,7 @@
         <v>45</v>
       </c>
       <c r="D521">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E521">
         <v>2</v>
@@ -16211,7 +16208,7 @@
         <v>514</v>
       </c>
       <c r="C523">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D523">
         <v>56</v>
@@ -16248,7 +16245,7 @@
         <v>44</v>
       </c>
       <c r="D525">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E525">
         <v>2</v>
@@ -16262,7 +16259,7 @@
         <v>517</v>
       </c>
       <c r="C526">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D526">
         <v>52</v>
@@ -16299,7 +16296,7 @@
         <v>47</v>
       </c>
       <c r="D528">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E528">
         <v>2</v>
@@ -16330,7 +16327,7 @@
         <v>521</v>
       </c>
       <c r="C530">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D530">
         <v>54</v>
@@ -16367,7 +16364,7 @@
         <v>48</v>
       </c>
       <c r="D532">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E532">
         <v>2</v>
@@ -16398,7 +16395,7 @@
         <v>525</v>
       </c>
       <c r="C534">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D534">
         <v>60</v>
@@ -16418,7 +16415,7 @@
         <v>46</v>
       </c>
       <c r="D535">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E535">
         <v>2</v>
@@ -16486,7 +16483,7 @@
         <v>46</v>
       </c>
       <c r="D539">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E539">
         <v>2</v>
@@ -16517,7 +16514,7 @@
         <v>532</v>
       </c>
       <c r="C541">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D541">
         <v>55</v>
@@ -16554,7 +16551,7 @@
         <v>48</v>
       </c>
       <c r="D543">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E543">
         <v>2</v>
@@ -16585,7 +16582,7 @@
         <v>536</v>
       </c>
       <c r="C545">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D545">
         <v>54</v>
@@ -16622,7 +16619,7 @@
         <v>46</v>
       </c>
       <c r="D547">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E547">
         <v>2</v>
@@ -16636,7 +16633,7 @@
         <v>539</v>
       </c>
       <c r="C548">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D548">
         <v>50</v>
@@ -16673,7 +16670,7 @@
         <v>43</v>
       </c>
       <c r="D550">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E550">
         <v>2</v>
@@ -16704,7 +16701,7 @@
         <v>543</v>
       </c>
       <c r="C552">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D552">
         <v>54</v>
@@ -16741,7 +16738,7 @@
         <v>44</v>
       </c>
       <c r="D554">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E554">
         <v>2</v>
@@ -16772,7 +16769,7 @@
         <v>547</v>
       </c>
       <c r="C556">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D556">
         <v>55</v>
@@ -16792,7 +16789,7 @@
         <v>46</v>
       </c>
       <c r="D557">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E557">
         <v>2</v>
@@ -16823,7 +16820,7 @@
         <v>550</v>
       </c>
       <c r="C559">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D559">
         <v>53</v>
@@ -16860,7 +16857,7 @@
         <v>47</v>
       </c>
       <c r="D561">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E561">
         <v>2</v>
@@ -16911,7 +16908,7 @@
         <v>47</v>
       </c>
       <c r="D564">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E564">
         <v>2</v>
@@ -16942,7 +16939,7 @@
         <v>557</v>
       </c>
       <c r="C566">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D566">
         <v>53</v>
@@ -16979,7 +16976,7 @@
         <v>48</v>
       </c>
       <c r="D568">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E568">
         <v>2</v>
@@ -17010,7 +17007,7 @@
         <v>561</v>
       </c>
       <c r="C570">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D570">
         <v>52</v>
@@ -17078,7 +17075,7 @@
         <v>565</v>
       </c>
       <c r="C574">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D574">
         <v>52</v>
@@ -17098,7 +17095,7 @@
         <v>41</v>
       </c>
       <c r="D575">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E575">
         <v>2</v>
@@ -17129,7 +17126,7 @@
         <v>568</v>
       </c>
       <c r="C577">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D577">
         <v>51</v>
@@ -17166,7 +17163,7 @@
         <v>43</v>
       </c>
       <c r="D579">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E579">
         <v>2</v>
@@ -17197,7 +17194,7 @@
         <v>572</v>
       </c>
       <c r="C581">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D581">
         <v>52</v>
@@ -17234,7 +17231,7 @@
         <v>48</v>
       </c>
       <c r="D583">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E583">
         <v>2</v>
@@ -17265,7 +17262,7 @@
         <v>576</v>
       </c>
       <c r="C585">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D585">
         <v>54</v>
@@ -17285,7 +17282,7 @@
         <v>49</v>
       </c>
       <c r="D586">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E586">
         <v>2</v>
@@ -17316,7 +17313,7 @@
         <v>579</v>
       </c>
       <c r="C588">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D588">
         <v>53</v>
@@ -17353,7 +17350,7 @@
         <v>43</v>
       </c>
       <c r="D590">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E590">
         <v>2</v>
@@ -17384,7 +17381,7 @@
         <v>583</v>
       </c>
       <c r="C592">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D592">
         <v>50</v>
@@ -17404,7 +17401,7 @@
         <v>45</v>
       </c>
       <c r="D593">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E593">
         <v>2</v>
@@ -17435,7 +17432,7 @@
         <v>586</v>
       </c>
       <c r="C595">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D595">
         <v>48</v>
@@ -17472,7 +17469,7 @@
         <v>48</v>
       </c>
       <c r="D597">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E597">
         <v>2</v>
@@ -17503,7 +17500,7 @@
         <v>590</v>
       </c>
       <c r="C599">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D599">
         <v>53</v>
@@ -17540,7 +17537,7 @@
         <v>46</v>
       </c>
       <c r="D601">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E601">
         <v>2</v>
@@ -17571,7 +17568,7 @@
         <v>594</v>
       </c>
       <c r="C603">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D603">
         <v>52</v>
@@ -17591,7 +17588,7 @@
         <v>43</v>
       </c>
       <c r="D604">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E604">
         <v>2</v>
@@ -17659,7 +17656,7 @@
         <v>43</v>
       </c>
       <c r="D608">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E608">
         <v>2</v>
@@ -17727,7 +17724,7 @@
         <v>43</v>
       </c>
       <c r="D612">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E612">
         <v>2</v>
@@ -17758,7 +17755,7 @@
         <v>605</v>
       </c>
       <c r="C614">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D614">
         <v>48</v>
@@ -17778,7 +17775,7 @@
         <v>45</v>
       </c>
       <c r="D615">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E615">
         <v>2</v>
@@ -17846,7 +17843,7 @@
         <v>45</v>
       </c>
       <c r="D619">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E619">
         <v>2</v>
@@ -17877,7 +17874,7 @@
         <v>612</v>
       </c>
       <c r="C621">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D621">
         <v>51</v>
@@ -17914,7 +17911,7 @@
         <v>44</v>
       </c>
       <c r="D623">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E623">
         <v>2</v>
@@ -17945,7 +17942,7 @@
         <v>616</v>
       </c>
       <c r="C625">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D625">
         <v>49</v>
@@ -17982,7 +17979,7 @@
         <v>46</v>
       </c>
       <c r="D627">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E627">
         <v>2</v>
@@ -17996,7 +17993,7 @@
         <v>619</v>
       </c>
       <c r="C628">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D628">
         <v>48</v>
@@ -18033,7 +18030,7 @@
         <v>44</v>
       </c>
       <c r="D630">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E630">
         <v>2</v>
@@ -18064,7 +18061,7 @@
         <v>623</v>
       </c>
       <c r="C632">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D632">
         <v>45</v>
@@ -18152,7 +18149,7 @@
         <v>39</v>
       </c>
       <c r="D637">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E637">
         <v>2</v>
@@ -18183,7 +18180,7 @@
         <v>630</v>
       </c>
       <c r="C639">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D639">
         <v>46</v>
@@ -18220,7 +18217,7 @@
         <v>42</v>
       </c>
       <c r="D641">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E641">
         <v>2</v>
@@ -18251,7 +18248,7 @@
         <v>634</v>
       </c>
       <c r="C643">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D643">
         <v>47</v>
@@ -18271,7 +18268,7 @@
         <v>43</v>
       </c>
       <c r="D644">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E644">
         <v>2</v>
@@ -18302,7 +18299,7 @@
         <v>637</v>
       </c>
       <c r="C646">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D646">
         <v>48</v>
@@ -18339,7 +18336,7 @@
         <v>41</v>
       </c>
       <c r="D648">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E648">
         <v>2</v>
@@ -18370,7 +18367,7 @@
         <v>641</v>
       </c>
       <c r="C650">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D650">
         <v>50</v>
@@ -18407,7 +18404,7 @@
         <v>39</v>
       </c>
       <c r="D652">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E652">
         <v>2</v>
@@ -18438,7 +18435,7 @@
         <v>645</v>
       </c>
       <c r="C654">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D654">
         <v>47</v>
@@ -18458,7 +18455,7 @@
         <v>41</v>
       </c>
       <c r="D655">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E655">
         <v>2</v>
@@ -18526,7 +18523,7 @@
         <v>41</v>
       </c>
       <c r="D659">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E659">
         <v>2</v>
@@ -18557,7 +18554,7 @@
         <v>652</v>
       </c>
       <c r="C661">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D661">
         <v>44</v>
@@ -18577,7 +18574,7 @@
         <v>40</v>
       </c>
       <c r="D662">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E662">
         <v>2</v>
@@ -18645,7 +18642,7 @@
         <v>40</v>
       </c>
       <c r="D666">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E666">
         <v>2</v>
@@ -18744,7 +18741,7 @@
         <v>663</v>
       </c>
       <c r="C672">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D672">
         <v>43</v>
@@ -18764,7 +18761,7 @@
         <v>41</v>
       </c>
       <c r="D673">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E673">
         <v>2</v>
@@ -18795,7 +18792,7 @@
         <v>666</v>
       </c>
       <c r="C675">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D675">
         <v>45</v>
@@ -18832,7 +18829,7 @@
         <v>39</v>
       </c>
       <c r="D677">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E677">
         <v>2</v>
@@ -18863,7 +18860,7 @@
         <v>670</v>
       </c>
       <c r="C679">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D679">
         <v>44</v>
@@ -18931,7 +18928,7 @@
         <v>674</v>
       </c>
       <c r="C683">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D683">
         <v>44</v>
@@ -18982,7 +18979,7 @@
         <v>677</v>
       </c>
       <c r="C686">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D686">
         <v>44</v>
@@ -19019,7 +19016,7 @@
         <v>45</v>
       </c>
       <c r="D688">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E688">
         <v>2</v>
@@ -19050,7 +19047,7 @@
         <v>681</v>
       </c>
       <c r="C690">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D690">
         <v>45</v>
@@ -19087,7 +19084,7 @@
         <v>42</v>
       </c>
       <c r="D692">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E692">
         <v>2</v>
@@ -19118,7 +19115,7 @@
         <v>685</v>
       </c>
       <c r="C694">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D694">
         <v>44</v>
@@ -19138,7 +19135,7 @@
         <v>40</v>
       </c>
       <c r="D695">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E695">
         <v>2</v>
@@ -19169,7 +19166,7 @@
         <v>688</v>
       </c>
       <c r="C697">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D697">
         <v>42</v>
@@ -19186,7 +19183,7 @@
         <v>689</v>
       </c>
       <c r="C698">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D698">
         <v>42</v>
@@ -19206,7 +19203,7 @@
         <v>40</v>
       </c>
       <c r="D699">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E699">
         <v>2</v>
@@ -19237,7 +19234,7 @@
         <v>692</v>
       </c>
       <c r="C701">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D701">
         <v>38</v>
@@ -19288,7 +19285,7 @@
         <v>695</v>
       </c>
       <c r="C704">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D704">
         <v>38</v>
@@ -19325,7 +19322,7 @@
         <v>38</v>
       </c>
       <c r="D706">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E706">
         <v>2</v>
@@ -19356,7 +19353,7 @@
         <v>699</v>
       </c>
       <c r="C708">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D708">
         <v>39</v>
@@ -19376,7 +19373,7 @@
         <v>39</v>
       </c>
       <c r="D709">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E709">
         <v>2</v>
@@ -19407,7 +19404,7 @@
         <v>702</v>
       </c>
       <c r="C711">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D711">
         <v>40</v>
@@ -19512,7 +19509,7 @@
         <v>40</v>
       </c>
       <c r="D717">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E717">
         <v>2</v>
@@ -19563,7 +19560,7 @@
         <v>40</v>
       </c>
       <c r="D720">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E720">
         <v>2</v>
@@ -19594,7 +19591,7 @@
         <v>713</v>
       </c>
       <c r="C722">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D722">
         <v>39</v>
@@ -19631,7 +19628,7 @@
         <v>39</v>
       </c>
       <c r="D724">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E724">
         <v>2</v>
@@ -19662,7 +19659,7 @@
         <v>717</v>
       </c>
       <c r="C726">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D726">
         <v>42</v>
@@ -19699,7 +19696,7 @@
         <v>43</v>
       </c>
       <c r="D728">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E728">
         <v>2</v>
@@ -19730,7 +19727,7 @@
         <v>721</v>
       </c>
       <c r="C730">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D730">
         <v>45</v>
@@ -19750,7 +19747,7 @@
         <v>40</v>
       </c>
       <c r="D731">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E731">
         <v>2</v>
@@ -19781,7 +19778,7 @@
         <v>724</v>
       </c>
       <c r="C733">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D733">
         <v>41</v>
@@ -19818,7 +19815,7 @@
         <v>36</v>
       </c>
       <c r="D735">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E735">
         <v>2</v>
@@ -19849,7 +19846,7 @@
         <v>728</v>
       </c>
       <c r="C737">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D737">
         <v>37</v>
@@ -19869,7 +19866,7 @@
         <v>39</v>
       </c>
       <c r="D738">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E738">
         <v>2</v>
@@ -19917,7 +19914,7 @@
         <v>732</v>
       </c>
       <c r="C741">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D741">
         <v>39</v>
@@ -19937,7 +19934,7 @@
         <v>41</v>
       </c>
       <c r="D742">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E742">
         <v>2</v>
@@ -19968,7 +19965,7 @@
         <v>735</v>
       </c>
       <c r="C744">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D744">
         <v>36</v>
@@ -20005,7 +20002,7 @@
         <v>36</v>
       </c>
       <c r="D746">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E746">
         <v>2</v>
@@ -20036,7 +20033,7 @@
         <v>739</v>
       </c>
       <c r="C748">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D748">
         <v>33</v>
@@ -20073,7 +20070,7 @@
         <v>34</v>
       </c>
       <c r="D750">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E750">
         <v>2</v>
@@ -20087,7 +20084,7 @@
         <v>742</v>
       </c>
       <c r="C751">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D751">
         <v>32</v>
@@ -20124,7 +20121,7 @@
         <v>35</v>
       </c>
       <c r="D753">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E753">
         <v>2</v>
@@ -20155,7 +20152,7 @@
         <v>746</v>
       </c>
       <c r="C755">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D755">
         <v>34</v>
@@ -20192,7 +20189,7 @@
         <v>34</v>
       </c>
       <c r="D757">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E757">
         <v>2</v>
@@ -20223,7 +20220,7 @@
         <v>750</v>
       </c>
       <c r="C759">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D759">
         <v>35</v>
@@ -20243,7 +20240,7 @@
         <v>36</v>
       </c>
       <c r="D760">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E760">
         <v>2</v>
@@ -20274,7 +20271,7 @@
         <v>753</v>
       </c>
       <c r="C762">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D762">
         <v>32</v>
@@ -20291,7 +20288,7 @@
         <v>754</v>
       </c>
       <c r="C763">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D763">
         <v>32</v>
@@ -20311,7 +20308,7 @@
         <v>36</v>
       </c>
       <c r="D764">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E764">
         <v>2</v>
@@ -20342,7 +20339,7 @@
         <v>757</v>
       </c>
       <c r="C766">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D766">
         <v>34</v>
@@ -20379,7 +20376,7 @@
         <v>37</v>
       </c>
       <c r="D768">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E768">
         <v>2</v>
@@ -20430,7 +20427,7 @@
         <v>37</v>
       </c>
       <c r="D771">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E771">
         <v>2</v>
@@ -20461,7 +20458,7 @@
         <v>764</v>
       </c>
       <c r="C773">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D773">
         <v>39</v>
@@ -20498,7 +20495,7 @@
         <v>40</v>
       </c>
       <c r="D775">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E775">
         <v>2</v>
@@ -20529,7 +20526,7 @@
         <v>768</v>
       </c>
       <c r="C777">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D777">
         <v>37</v>
@@ -20549,7 +20546,7 @@
         <v>37</v>
       </c>
       <c r="D778">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E778">
         <v>2</v>
@@ -20580,7 +20577,7 @@
         <v>771</v>
       </c>
       <c r="C780">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D780">
         <v>35</v>
@@ -20634,7 +20631,7 @@
         <v>35</v>
       </c>
       <c r="D783">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E783">
         <v>2</v>
@@ -20648,7 +20645,7 @@
         <v>775</v>
       </c>
       <c r="C784">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D784">
         <v>31</v>
@@ -20685,7 +20682,7 @@
         <v>34</v>
       </c>
       <c r="D786">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E786">
         <v>2</v>
@@ -20716,7 +20713,7 @@
         <v>779</v>
       </c>
       <c r="C788">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D788">
         <v>32</v>
@@ -20736,7 +20733,7 @@
         <v>32</v>
       </c>
       <c r="D789">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E789">
         <v>2</v>
@@ -20767,7 +20764,7 @@
         <v>782</v>
       </c>
       <c r="C791">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D791">
         <v>31</v>
@@ -20804,7 +20801,7 @@
         <v>36</v>
       </c>
       <c r="D793">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E793">
         <v>2</v>
@@ -20903,7 +20900,7 @@
         <v>790</v>
       </c>
       <c r="C799">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D799">
         <v>36</v>
@@ -20923,7 +20920,7 @@
         <v>35</v>
       </c>
       <c r="D800">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E800">
         <v>2</v>
@@ -20991,7 +20988,7 @@
         <v>35</v>
       </c>
       <c r="D804">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E804">
         <v>2</v>
@@ -21059,7 +21056,7 @@
         <v>35</v>
       </c>
       <c r="D808">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E808">
         <v>2</v>
@@ -21090,7 +21087,7 @@
         <v>801</v>
       </c>
       <c r="C810">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D810">
         <v>28</v>
@@ -21110,7 +21107,7 @@
         <v>37</v>
       </c>
       <c r="D811">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E811">
         <v>2</v>
@@ -21141,7 +21138,7 @@
         <v>804</v>
       </c>
       <c r="C813">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D813">
         <v>29</v>
@@ -21178,7 +21175,7 @@
         <v>35</v>
       </c>
       <c r="D815">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E815">
         <v>2</v>
@@ -21209,7 +21206,7 @@
         <v>808</v>
       </c>
       <c r="C817">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D817">
         <v>32</v>
@@ -21229,7 +21226,7 @@
         <v>39</v>
       </c>
       <c r="D818">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E818">
         <v>2</v>
@@ -21297,7 +21294,7 @@
         <v>39</v>
       </c>
       <c r="D822">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E822">
         <v>2</v>
@@ -21328,7 +21325,7 @@
         <v>815</v>
       </c>
       <c r="C824">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D824">
         <v>34</v>
@@ -21365,7 +21362,7 @@
         <v>37</v>
       </c>
       <c r="D826">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E826">
         <v>2</v>
@@ -21396,7 +21393,7 @@
         <v>819</v>
       </c>
       <c r="C828">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D828">
         <v>32</v>
@@ -21416,7 +21413,7 @@
         <v>35</v>
       </c>
       <c r="D829">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E829">
         <v>2</v>
@@ -21447,7 +21444,7 @@
         <v>822</v>
       </c>
       <c r="C831">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D831">
         <v>29</v>
@@ -21484,7 +21481,7 @@
         <v>34</v>
       </c>
       <c r="D833">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E833">
         <v>2</v>
@@ -21515,7 +21512,7 @@
         <v>826</v>
       </c>
       <c r="C835">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D835">
         <v>28</v>
@@ -21552,7 +21549,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E837">
         <v>2</v>
@@ -21583,7 +21580,7 @@
         <v>830</v>
       </c>
       <c r="C839">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D839">
         <v>25</v>
@@ -21603,7 +21600,7 @@
         <v>33</v>
       </c>
       <c r="D840">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E840">
         <v>2</v>
@@ -21634,7 +21631,7 @@
         <v>833</v>
       </c>
       <c r="C842">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D842">
         <v>27</v>
@@ -21671,7 +21668,7 @@
         <v>34</v>
       </c>
       <c r="D844">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E844">
         <v>2</v>
@@ -21702,7 +21699,7 @@
         <v>837</v>
       </c>
       <c r="C846">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D846">
         <v>30</v>
@@ -21753,7 +21750,7 @@
         <v>840</v>
       </c>
       <c r="C849">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D849">
         <v>30</v>
@@ -21790,7 +21787,7 @@
         <v>35</v>
       </c>
       <c r="D851">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E851">
         <v>2</v>
@@ -21858,7 +21855,7 @@
         <v>35</v>
       </c>
       <c r="D855">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E855">
         <v>2</v>
@@ -21940,7 +21937,7 @@
         <v>851</v>
       </c>
       <c r="C860">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D860">
         <v>28</v>
@@ -21977,7 +21974,7 @@
         <v>34</v>
       </c>
       <c r="D862">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E862">
         <v>2</v>
@@ -22008,7 +22005,7 @@
         <v>855</v>
       </c>
       <c r="C864">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D864">
         <v>31</v>
@@ -22045,7 +22042,7 @@
         <v>35</v>
       </c>
       <c r="D866">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E866">
         <v>2</v>
@@ -22076,7 +22073,7 @@
         <v>859</v>
       </c>
       <c r="C868">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D868">
         <v>28</v>
@@ -22096,7 +22093,7 @@
         <v>32</v>
       </c>
       <c r="D869">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E869">
         <v>2</v>
@@ -22127,7 +22124,7 @@
         <v>862</v>
       </c>
       <c r="C871">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D871">
         <v>27</v>
@@ -22161,10 +22158,10 @@
         <v>864</v>
       </c>
       <c r="C873">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D873">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E873">
         <v>2</v>
@@ -22178,7 +22175,7 @@
         <v>865</v>
       </c>
       <c r="C874">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D874">
         <v>30</v>
@@ -22195,7 +22192,7 @@
         <v>866</v>
       </c>
       <c r="C875">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D875">
         <v>30</v>
@@ -22215,7 +22212,7 @@
         <v>30</v>
       </c>
       <c r="D876">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E876">
         <v>2</v>
@@ -22263,7 +22260,7 @@
         <v>870</v>
       </c>
       <c r="C879">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D879">
         <v>29</v>
@@ -22283,7 +22280,7 @@
         <v>36</v>
       </c>
       <c r="D880">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E880">
         <v>2</v>
@@ -22314,7 +22311,7 @@
         <v>873</v>
       </c>
       <c r="C882">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D882">
         <v>30</v>
@@ -22351,7 +22348,7 @@
         <v>38</v>
       </c>
       <c r="D884">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E884">
         <v>2</v>
@@ -22382,7 +22379,7 @@
         <v>877</v>
       </c>
       <c r="C886">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D886">
         <v>28</v>
@@ -22402,7 +22399,7 @@
         <v>34</v>
       </c>
       <c r="D887">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E887">
         <v>2</v>
@@ -22433,7 +22430,7 @@
         <v>880</v>
       </c>
       <c r="C889">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D889">
         <v>30</v>
@@ -22470,7 +22467,7 @@
         <v>33</v>
       </c>
       <c r="D891">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E891">
         <v>2</v>
@@ -22538,7 +22535,7 @@
         <v>33</v>
       </c>
       <c r="D895">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E895">
         <v>2</v>
@@ -22569,7 +22566,7 @@
         <v>888</v>
       </c>
       <c r="C897">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D897">
         <v>25</v>
@@ -22589,7 +22586,7 @@
         <v>32</v>
       </c>
       <c r="D898">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E898">
         <v>2</v>
@@ -22620,7 +22617,7 @@
         <v>891</v>
       </c>
       <c r="C900">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D900">
         <v>26</v>
@@ -22657,7 +22654,7 @@
         <v>35</v>
       </c>
       <c r="D902">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E902">
         <v>2</v>
@@ -22688,7 +22685,7 @@
         <v>895</v>
       </c>
       <c r="C904">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D904">
         <v>24</v>
@@ -22725,7 +22722,7 @@
         <v>33</v>
       </c>
       <c r="D906">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E906">
         <v>2</v>
@@ -22756,7 +22753,7 @@
         <v>899</v>
       </c>
       <c r="C908">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D908">
         <v>26</v>
@@ -22807,7 +22804,7 @@
         <v>902</v>
       </c>
       <c r="C911">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D911">
         <v>26</v>
@@ -22844,7 +22841,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E913">
         <v>2</v>
@@ -22875,7 +22872,7 @@
         <v>906</v>
       </c>
       <c r="C915">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D915">
         <v>27</v>
@@ -22895,7 +22892,7 @@
         <v>31</v>
       </c>
       <c r="D916">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E916">
         <v>2</v>
@@ -22926,7 +22923,7 @@
         <v>909</v>
       </c>
       <c r="C918">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D918">
         <v>29</v>
@@ -22963,7 +22960,7 @@
         <v>37</v>
       </c>
       <c r="D920">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E920">
         <v>2</v>
@@ -22994,7 +22991,7 @@
         <v>913</v>
       </c>
       <c r="C922">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D922">
         <v>30</v>
@@ -23031,7 +23028,7 @@
         <v>35</v>
       </c>
       <c r="D924">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E924">
         <v>2</v>
@@ -23062,7 +23059,7 @@
         <v>917</v>
       </c>
       <c r="C926">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D926">
         <v>26</v>
@@ -23082,7 +23079,7 @@
         <v>32</v>
       </c>
       <c r="D927">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E927">
         <v>2</v>
@@ -23113,7 +23110,7 @@
         <v>920</v>
       </c>
       <c r="C929">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D929">
         <v>25</v>
@@ -23181,7 +23178,7 @@
         <v>924</v>
       </c>
       <c r="C933">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D933">
         <v>25</v>
@@ -23218,7 +23215,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E935">
         <v>2</v>
@@ -23249,7 +23246,7 @@
         <v>928</v>
       </c>
       <c r="C937">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D937">
         <v>22</v>
@@ -23269,7 +23266,7 @@
         <v>30</v>
       </c>
       <c r="D938">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E938">
         <v>2</v>
@@ -23300,7 +23297,7 @@
         <v>931</v>
       </c>
       <c r="C940">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D940">
         <v>24</v>
@@ -23337,7 +23334,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E942">
         <v>2</v>
@@ -23368,7 +23365,7 @@
         <v>935</v>
       </c>
       <c r="C944">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D944">
         <v>25</v>
@@ -23405,7 +23402,7 @@
         <v>32</v>
       </c>
       <c r="D946">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E946">
         <v>2</v>
@@ -23456,7 +23453,7 @@
         <v>32</v>
       </c>
       <c r="D949">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E949">
         <v>2</v>
@@ -23487,7 +23484,7 @@
         <v>942</v>
       </c>
       <c r="C951">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D951">
         <v>23</v>
@@ -23524,7 +23521,7 @@
         <v>35</v>
       </c>
       <c r="D953">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E953">
         <v>2</v>
@@ -23555,7 +23552,7 @@
         <v>946</v>
       </c>
       <c r="C955">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D955">
         <v>27</v>
@@ -23606,7 +23603,7 @@
         <v>949</v>
       </c>
       <c r="C958">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D958">
         <v>27</v>
@@ -23643,7 +23640,7 @@
         <v>35</v>
       </c>
       <c r="D960">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E960">
         <v>2</v>
@@ -23674,7 +23671,7 @@
         <v>953</v>
       </c>
       <c r="C962">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D962">
         <v>26</v>
@@ -23711,7 +23708,7 @@
         <v>32</v>
       </c>
       <c r="D964">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E964">
         <v>2</v>
@@ -23742,7 +23739,7 @@
         <v>957</v>
       </c>
       <c r="C966">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D966">
         <v>23</v>
@@ -23861,7 +23858,7 @@
         <v>964</v>
       </c>
       <c r="C973">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D973">
         <v>23</v>
@@ -23898,7 +23895,7 @@
         <v>28</v>
       </c>
       <c r="D975">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E975">
         <v>2</v>
@@ -23929,7 +23926,7 @@
         <v>968</v>
       </c>
       <c r="C977">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D977">
         <v>25</v>
@@ -23949,7 +23946,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E978">
         <v>2</v>
@@ -23980,7 +23977,7 @@
         <v>971</v>
       </c>
       <c r="C980">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D980">
         <v>24</v>
@@ -24017,7 +24014,7 @@
         <v>34</v>
       </c>
       <c r="D982">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E982">
         <v>2</v>
@@ -24048,7 +24045,7 @@
         <v>975</v>
       </c>
       <c r="C984">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D984">
         <v>30</v>
@@ -24068,7 +24065,7 @@
         <v>33</v>
       </c>
       <c r="D985">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E985">
         <v>2</v>
@@ -24153,7 +24150,7 @@
         <v>33</v>
       </c>
       <c r="D990">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E990">
         <v>2</v>
@@ -24167,7 +24164,7 @@
         <v>982</v>
       </c>
       <c r="C991">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D991">
         <v>24</v>
@@ -24204,7 +24201,7 @@
         <v>31</v>
       </c>
       <c r="D993">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E993">
         <v>2</v>
@@ -24255,7 +24252,7 @@
         <v>31</v>
       </c>
       <c r="D996">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E996">
         <v>2</v>
@@ -24286,7 +24283,7 @@
         <v>989</v>
       </c>
       <c r="C998">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D998">
         <v>24</v>
@@ -24323,7 +24320,7 @@
         <v>30</v>
       </c>
       <c r="D1000">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1000">
         <v>2</v>
@@ -24391,7 +24388,7 @@
         <v>30</v>
       </c>
       <c r="D1004">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E1004">
         <v>2</v>
@@ -24422,7 +24419,7 @@
         <v>997</v>
       </c>
       <c r="C1006">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1006">
         <v>23</v>
@@ -24442,7 +24439,7 @@
         <v>32</v>
       </c>
       <c r="D1007">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1007">
         <v>2</v>
@@ -24473,7 +24470,7 @@
         <v>1000</v>
       </c>
       <c r="C1009">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1009">
         <v>26</v>
@@ -24510,7 +24507,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1011">
         <v>2</v>
@@ -24578,7 +24575,7 @@
         <v>29</v>
       </c>
       <c r="D1015">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E1015">
         <v>2</v>
@@ -24629,7 +24626,7 @@
         <v>29</v>
       </c>
       <c r="D1018">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E1018">
         <v>2</v>
@@ -24660,7 +24657,7 @@
         <v>1011</v>
       </c>
       <c r="C1020">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D1020">
         <v>20</v>
@@ -24728,7 +24725,7 @@
         <v>1015</v>
       </c>
       <c r="C1024">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D1024">
         <v>20</v>
@@ -24748,7 +24745,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E1025">
         <v>2</v>
@@ -24779,7 +24776,7 @@
         <v>1018</v>
       </c>
       <c r="C1027">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D1027">
         <v>22</v>
@@ -24847,7 +24844,7 @@
         <v>1022</v>
       </c>
       <c r="C1031">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D1031">
         <v>22</v>
@@ -24884,7 +24881,7 @@
         <v>34</v>
       </c>
       <c r="D1033">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E1033">
         <v>2</v>
@@ -24932,7 +24929,7 @@
         <v>1027</v>
       </c>
       <c r="C1036">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D1036">
         <v>25</v>
@@ -24966,7 +24963,7 @@
         <v>1029</v>
       </c>
       <c r="C1038">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1038">
         <v>25</v>
@@ -25003,7 +25000,7 @@
         <v>30</v>
       </c>
       <c r="D1040">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E1040">
         <v>2</v>
@@ -25034,7 +25031,7 @@
         <v>1033</v>
       </c>
       <c r="C1042">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D1042">
         <v>22</v>
@@ -25071,7 +25068,7 @@
         <v>28</v>
       </c>
       <c r="D1044">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E1044">
         <v>2</v>
@@ -25102,7 +25099,7 @@
         <v>1037</v>
       </c>
       <c r="C1046">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1046">
         <v>20</v>
@@ -25122,7 +25119,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1047">
         <v>2</v>
@@ -25153,7 +25150,7 @@
         <v>1040</v>
       </c>
       <c r="C1049">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1049">
         <v>17</v>
@@ -25190,7 +25187,7 @@
         <v>30</v>
       </c>
       <c r="D1051">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1051">
         <v>2</v>
@@ -25221,7 +25218,7 @@
         <v>1044</v>
       </c>
       <c r="C1053">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D1053">
         <v>21</v>
@@ -25241,7 +25238,7 @@
         <v>28</v>
       </c>
       <c r="D1054">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1054">
         <v>2</v>
@@ -25309,7 +25306,7 @@
         <v>28</v>
       </c>
       <c r="D1058">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E1058">
         <v>2</v>
@@ -25340,7 +25337,7 @@
         <v>1051</v>
       </c>
       <c r="C1060">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1060">
         <v>24</v>
@@ -25377,7 +25374,7 @@
         <v>30</v>
       </c>
       <c r="D1062">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1062">
         <v>2</v>
@@ -25408,7 +25405,7 @@
         <v>1055</v>
       </c>
       <c r="C1064">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1064">
         <v>26</v>
@@ -25428,7 +25425,7 @@
         <v>32</v>
       </c>
       <c r="D1065">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E1065">
         <v>2</v>
@@ -25459,7 +25456,7 @@
         <v>1058</v>
       </c>
       <c r="C1067">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1067">
         <v>22</v>
@@ -25527,7 +25524,7 @@
         <v>1062</v>
       </c>
       <c r="C1071">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D1071">
         <v>22</v>
@@ -25564,7 +25561,7 @@
         <v>31</v>
       </c>
       <c r="D1073">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1073">
         <v>2</v>
@@ -25595,7 +25592,7 @@
         <v>1066</v>
       </c>
       <c r="C1075">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1075">
         <v>21</v>
@@ -25615,7 +25612,7 @@
         <v>30</v>
       </c>
       <c r="D1076">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E1076">
         <v>2</v>
@@ -25646,7 +25643,7 @@
         <v>1069</v>
       </c>
       <c r="C1078">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1078">
         <v>24</v>
@@ -25683,7 +25680,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E1080">
         <v>2</v>
@@ -25714,7 +25711,7 @@
         <v>1073</v>
       </c>
       <c r="C1082">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1082">
         <v>22</v>
@@ -25751,7 +25748,7 @@
         <v>28</v>
       </c>
       <c r="D1084">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E1084">
         <v>2</v>
@@ -25782,7 +25779,7 @@
         <v>1077</v>
       </c>
       <c r="C1086">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1086">
         <v>19</v>
@@ -25819,7 +25816,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E1088">
         <v>2</v>
@@ -25833,7 +25830,7 @@
         <v>1080</v>
       </c>
       <c r="C1089">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1089">
         <v>22</v>
@@ -25870,7 +25867,7 @@
         <v>30</v>
       </c>
       <c r="D1091">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E1091">
         <v>2</v>
@@ -25951,9 +25948,6 @@
       <c r="B1096" t="s">
         <v>1087</v>
       </c>
-      <c r="C1096">
-        <v>30</v>
-      </c>
       <c r="D1096">
         <v>20</v>
       </c>
@@ -25983,7 +25977,7 @@
         <v>1089</v>
       </c>
       <c r="D1098">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1098">
         <v>2</v>
@@ -26039,7 +26033,7 @@
         <v>1093</v>
       </c>
       <c r="D1102">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1102">
         <v>2</v>
@@ -26081,7 +26075,7 @@
         <v>1096</v>
       </c>
       <c r="D1105">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1105">
         <v>2</v>
@@ -26137,7 +26131,7 @@
         <v>1100</v>
       </c>
       <c r="D1109">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1109">
         <v>2</v>
@@ -26193,7 +26187,7 @@
         <v>1104</v>
       </c>
       <c r="D1113">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1113">
         <v>2</v>
@@ -26235,7 +26229,7 @@
         <v>1107</v>
       </c>
       <c r="D1116">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1116">
         <v>2</v>
@@ -26291,7 +26285,7 @@
         <v>1111</v>
       </c>
       <c r="D1120">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1120">
         <v>2</v>
@@ -26333,7 +26327,7 @@
         <v>1114</v>
       </c>
       <c r="D1123">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1123">
         <v>2</v>
@@ -26389,7 +26383,7 @@
         <v>1118</v>
       </c>
       <c r="D1127">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1127">
         <v>2</v>
@@ -26445,7 +26439,7 @@
         <v>1122</v>
       </c>
       <c r="D1131">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1131">
         <v>2</v>
@@ -26487,7 +26481,7 @@
         <v>1125</v>
       </c>
       <c r="D1134">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1134">
         <v>2</v>
@@ -26543,7 +26537,7 @@
         <v>1129</v>
       </c>
       <c r="D1138">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1138">
         <v>2</v>
@@ -26599,7 +26593,7 @@
         <v>1133</v>
       </c>
       <c r="D1142">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1142">
         <v>2</v>
@@ -26697,7 +26691,7 @@
         <v>1140</v>
       </c>
       <c r="D1149">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1149">
         <v>2</v>
@@ -26739,7 +26733,7 @@
         <v>1143</v>
       </c>
       <c r="D1152">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1152">
         <v>2</v>
@@ -26795,7 +26789,7 @@
         <v>1147</v>
       </c>
       <c r="D1156">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1156">
         <v>2</v>
@@ -26822,6 +26816,9 @@
       <c r="B1158" t="s">
         <v>1149</v>
       </c>
+      <c r="C1158">
+        <v>28</v>
+      </c>
       <c r="D1158">
         <v>15</v>
       </c>
@@ -26857,7 +26854,7 @@
         <v>28</v>
       </c>
       <c r="D1160">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1160">
         <v>2</v>
@@ -26908,7 +26905,7 @@
         <v>28</v>
       </c>
       <c r="D1163">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1163">
         <v>2</v>
@@ -26939,7 +26936,7 @@
         <v>1156</v>
       </c>
       <c r="C1165">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1165">
         <v>18</v>
@@ -26976,7 +26973,7 @@
         <v>26</v>
       </c>
       <c r="D1167">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1167">
         <v>2</v>
@@ -27058,7 +27055,7 @@
         <v>1163</v>
       </c>
       <c r="C1172">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1172">
         <v>14</v>
@@ -27095,7 +27092,7 @@
         <v>28</v>
       </c>
       <c r="D1174">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1174">
         <v>2</v>
@@ -27126,7 +27123,7 @@
         <v>1167</v>
       </c>
       <c r="C1176">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1176">
         <v>17</v>
@@ -27163,7 +27160,7 @@
         <v>27</v>
       </c>
       <c r="D1178">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1178">
         <v>2</v>
@@ -27194,7 +27191,7 @@
         <v>1171</v>
       </c>
       <c r="C1180">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1180">
         <v>16</v>
@@ -27214,7 +27211,7 @@
         <v>26</v>
       </c>
       <c r="D1181">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1181">
         <v>2</v>
@@ -27245,7 +27242,7 @@
         <v>1174</v>
       </c>
       <c r="C1183">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D1183">
         <v>14</v>
@@ -27282,7 +27279,7 @@
         <v>23</v>
       </c>
       <c r="D1185">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1185">
         <v>2</v>
@@ -27313,7 +27310,7 @@
         <v>1178</v>
       </c>
       <c r="C1187">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D1187">
         <v>15</v>
@@ -27350,7 +27347,7 @@
         <v>25</v>
       </c>
       <c r="D1189">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1189">
         <v>2</v>
@@ -27381,7 +27378,7 @@
         <v>1182</v>
       </c>
       <c r="C1191">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1191">
         <v>16</v>
@@ -27469,7 +27466,7 @@
         <v>26</v>
       </c>
       <c r="D1196">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1196">
         <v>2</v>
@@ -27520,7 +27517,7 @@
         <v>26</v>
       </c>
       <c r="D1199">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1199">
         <v>2</v>
@@ -27551,7 +27548,7 @@
         <v>1192</v>
       </c>
       <c r="C1201">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1201">
         <v>16</v>
@@ -27588,7 +27585,7 @@
         <v>25</v>
       </c>
       <c r="D1203">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1203">
         <v>2</v>
@@ -27619,7 +27616,7 @@
         <v>1196</v>
       </c>
       <c r="C1205">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1205">
         <v>17</v>
@@ -27656,7 +27653,7 @@
         <v>23</v>
       </c>
       <c r="D1207">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1207">
         <v>2</v>
@@ -27687,7 +27684,7 @@
         <v>1200</v>
       </c>
       <c r="C1209">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1209">
         <v>15</v>
@@ -27738,7 +27735,7 @@
         <v>1203</v>
       </c>
       <c r="C1212">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1212">
         <v>15</v>
@@ -27775,7 +27772,7 @@
         <v>23</v>
       </c>
       <c r="D1214">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1214">
         <v>2</v>
@@ -27843,7 +27840,7 @@
         <v>23</v>
       </c>
       <c r="D1218">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1218">
         <v>2</v>
@@ -27894,7 +27891,7 @@
         <v>23</v>
       </c>
       <c r="D1221">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1221">
         <v>2</v>
@@ -27959,10 +27956,10 @@
         <v>1216</v>
       </c>
       <c r="C1225">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D1225">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E1225">
         <v>2</v>
@@ -28030,7 +28027,7 @@
         <v>0</v>
       </c>
       <c r="D1229">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1229">
         <v>2</v>
@@ -28044,7 +28041,7 @@
         <v>1221</v>
       </c>
       <c r="C1230">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D1230">
         <v>15</v>
@@ -28061,7 +28058,7 @@
         <v>1222</v>
       </c>
       <c r="C1231">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1231">
         <v>15</v>
@@ -28081,7 +28078,7 @@
         <v>25</v>
       </c>
       <c r="D1232">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1232">
         <v>2</v>
@@ -28112,7 +28109,7 @@
         <v>1225</v>
       </c>
       <c r="C1234">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1234">
         <v>14</v>
@@ -28149,7 +28146,7 @@
         <v>24</v>
       </c>
       <c r="D1236">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1236">
         <v>2</v>
@@ -28180,7 +28177,7 @@
         <v>1229</v>
       </c>
       <c r="C1238">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1238">
         <v>15</v>
@@ -28231,7 +28228,7 @@
         <v>1232</v>
       </c>
       <c r="C1241">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1241">
         <v>15</v>
@@ -28268,7 +28265,7 @@
         <v>22</v>
       </c>
       <c r="D1243">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1243">
         <v>2</v>
@@ -28299,7 +28296,7 @@
         <v>1236</v>
       </c>
       <c r="C1245">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D1245">
         <v>14</v>
@@ -28336,7 +28333,7 @@
         <v>0</v>
       </c>
       <c r="D1247">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1247">
         <v>2</v>
@@ -28367,7 +28364,7 @@
         <v>1240</v>
       </c>
       <c r="C1249">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D1249">
         <v>15</v>
@@ -28418,7 +28415,7 @@
         <v>1243</v>
       </c>
       <c r="C1252">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D1252">
         <v>15</v>
@@ -28455,7 +28452,7 @@
         <v>0</v>
       </c>
       <c r="D1254">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1254">
         <v>2</v>
@@ -28486,7 +28483,7 @@
         <v>1247</v>
       </c>
       <c r="C1256">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D1256">
         <v>12</v>
@@ -28523,7 +28520,7 @@
         <v>23</v>
       </c>
       <c r="D1258">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1258">
         <v>2</v>
@@ -28554,7 +28551,7 @@
         <v>1251</v>
       </c>
       <c r="C1260">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1260">
         <v>14</v>
@@ -28574,7 +28571,7 @@
         <v>21</v>
       </c>
       <c r="D1261">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1261">
         <v>2</v>
@@ -28642,7 +28639,7 @@
         <v>21</v>
       </c>
       <c r="D1265">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1265">
         <v>2</v>
@@ -28673,7 +28670,7 @@
         <v>1258</v>
       </c>
       <c r="C1267">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1267">
         <v>15</v>
@@ -28710,7 +28707,7 @@
         <v>22</v>
       </c>
       <c r="D1269">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1269">
         <v>2</v>
@@ -28741,7 +28738,7 @@
         <v>1262</v>
       </c>
       <c r="C1271">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1271">
         <v>13</v>
@@ -28792,7 +28789,7 @@
         <v>1265</v>
       </c>
       <c r="C1274">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1274">
         <v>13</v>
@@ -28829,7 +28826,7 @@
         <v>22</v>
       </c>
       <c r="D1276">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1276">
         <v>2</v>
@@ -28860,7 +28857,7 @@
         <v>1269</v>
       </c>
       <c r="C1278">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1278">
         <v>15</v>
@@ -28911,7 +28908,7 @@
         <v>1272</v>
       </c>
       <c r="C1281">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1281">
         <v>15</v>
@@ -28948,7 +28945,7 @@
         <v>21</v>
       </c>
       <c r="D1283">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1283">
         <v>2</v>
@@ -28979,7 +28976,7 @@
         <v>1276</v>
       </c>
       <c r="C1285">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D1285">
         <v>13</v>
@@ -29016,7 +29013,7 @@
         <v>24</v>
       </c>
       <c r="D1287">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1287">
         <v>2</v>
@@ -29067,7 +29064,7 @@
         <v>24</v>
       </c>
       <c r="D1290">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1290">
         <v>2</v>
@@ -29098,7 +29095,7 @@
         <v>1283</v>
       </c>
       <c r="C1292">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1292">
         <v>11</v>
@@ -29135,7 +29132,7 @@
         <v>23</v>
       </c>
       <c r="D1294">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1294">
         <v>2</v>
@@ -29166,7 +29163,7 @@
         <v>1287</v>
       </c>
       <c r="C1296">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1296">
         <v>13</v>
@@ -29203,7 +29200,7 @@
         <v>21</v>
       </c>
       <c r="D1298">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1298">
         <v>2</v>
@@ -29234,7 +29231,7 @@
         <v>1291</v>
       </c>
       <c r="C1300">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1300">
         <v>11</v>
@@ -29254,7 +29251,7 @@
         <v>22</v>
       </c>
       <c r="D1301">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1301">
         <v>2</v>
@@ -29285,7 +29282,7 @@
         <v>1294</v>
       </c>
       <c r="C1303">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D1303">
         <v>13</v>
@@ -29322,7 +29319,7 @@
         <v>18</v>
       </c>
       <c r="D1305">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1305">
         <v>2</v>
@@ -29353,7 +29350,7 @@
         <v>1298</v>
       </c>
       <c r="C1307">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1307">
         <v>14</v>
@@ -29373,7 +29370,7 @@
         <v>20</v>
       </c>
       <c r="D1308">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1308">
         <v>2</v>
@@ -29404,7 +29401,7 @@
         <v>1301</v>
       </c>
       <c r="C1310">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1310">
         <v>12</v>
@@ -29472,7 +29469,7 @@
         <v>1305</v>
       </c>
       <c r="C1314">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1314">
         <v>12</v>
@@ -29509,7 +29506,7 @@
         <v>22</v>
       </c>
       <c r="D1316">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1316">
         <v>2</v>
@@ -29540,7 +29537,7 @@
         <v>1309</v>
       </c>
       <c r="C1318">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1318">
         <v>13</v>
@@ -29591,7 +29588,7 @@
         <v>1312</v>
       </c>
       <c r="C1321">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1321">
         <v>13</v>
@@ -29628,7 +29625,7 @@
         <v>21</v>
       </c>
       <c r="D1323">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1323">
         <v>2</v>
@@ -29659,7 +29656,7 @@
         <v>1316</v>
       </c>
       <c r="C1325">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D1325">
         <v>11</v>
@@ -29696,7 +29693,7 @@
         <v>19</v>
       </c>
       <c r="D1327">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1327">
         <v>2</v>
@@ -29727,7 +29724,7 @@
         <v>1320</v>
       </c>
       <c r="C1329">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1329">
         <v>14</v>
@@ -29747,7 +29744,7 @@
         <v>18</v>
       </c>
       <c r="D1330">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1330">
         <v>2</v>
@@ -29778,7 +29775,7 @@
         <v>1323</v>
       </c>
       <c r="C1332">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1332">
         <v>12</v>
@@ -29815,7 +29812,7 @@
         <v>21</v>
       </c>
       <c r="D1334">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1334">
         <v>2</v>
@@ -29846,7 +29843,7 @@
         <v>1327</v>
       </c>
       <c r="C1336">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D1336">
         <v>13</v>
@@ -29897,7 +29894,7 @@
         <v>1330</v>
       </c>
       <c r="C1339">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1339">
         <v>13</v>
@@ -29934,7 +29931,7 @@
         <v>21</v>
       </c>
       <c r="D1341">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1341">
         <v>2</v>
@@ -29965,7 +29962,7 @@
         <v>1334</v>
       </c>
       <c r="C1343">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D1343">
         <v>15</v>
@@ -30002,7 +29999,7 @@
         <v>18</v>
       </c>
       <c r="D1345">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1345">
         <v>2</v>
@@ -30053,7 +30050,7 @@
         <v>18</v>
       </c>
       <c r="D1348">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1348">
         <v>2</v>
@@ -30121,7 +30118,7 @@
         <v>18</v>
       </c>
       <c r="D1352">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1352">
         <v>2</v>
@@ -30189,7 +30186,7 @@
         <v>18</v>
       </c>
       <c r="D1356">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1356">
         <v>2</v>
@@ -30220,7 +30217,7 @@
         <v>1349</v>
       </c>
       <c r="C1358">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1358">
         <v>10</v>
@@ -30240,7 +30237,7 @@
         <v>19</v>
       </c>
       <c r="D1359">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1359">
         <v>2</v>
@@ -30288,7 +30285,7 @@
         <v>1353</v>
       </c>
       <c r="C1362">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1362">
         <v>12</v>
@@ -30308,7 +30305,7 @@
         <v>18</v>
       </c>
       <c r="D1363">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1363">
         <v>2</v>
@@ -30339,7 +30336,7 @@
         <v>1356</v>
       </c>
       <c r="C1365">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1365">
         <v>13</v>
@@ -30407,7 +30404,7 @@
         <v>1360</v>
       </c>
       <c r="C1369">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D1369">
         <v>13</v>
@@ -30427,7 +30424,7 @@
         <v>16</v>
       </c>
       <c r="D1370">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1370">
         <v>2</v>
@@ -30458,7 +30455,7 @@
         <v>1363</v>
       </c>
       <c r="C1372">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1372">
         <v>11</v>
@@ -30495,7 +30492,7 @@
         <v>18</v>
       </c>
       <c r="D1374">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1374">
         <v>2</v>
@@ -30546,7 +30543,7 @@
         <v>18</v>
       </c>
       <c r="D1377">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1377">
         <v>2</v>
@@ -30577,7 +30574,7 @@
         <v>1370</v>
       </c>
       <c r="C1379">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1379">
         <v>13</v>
@@ -30645,7 +30642,7 @@
         <v>1374</v>
       </c>
       <c r="C1383">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D1383">
         <v>13</v>
@@ -30713,7 +30710,7 @@
         <v>1378</v>
       </c>
       <c r="C1387">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1387">
         <v>13</v>
@@ -30733,7 +30730,7 @@
         <v>17</v>
       </c>
       <c r="D1388">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1388">
         <v>2</v>
@@ -30764,7 +30761,7 @@
         <v>1381</v>
       </c>
       <c r="C1390">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1390">
         <v>14</v>
@@ -30869,7 +30866,7 @@
         <v>19</v>
       </c>
       <c r="D1396">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1396">
         <v>2</v>
@@ -30900,7 +30897,7 @@
         <v>1389</v>
       </c>
       <c r="C1398">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1398">
         <v>10</v>
@@ -30937,7 +30934,7 @@
         <v>18</v>
       </c>
       <c r="D1400">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1400">
         <v>2</v>
@@ -30951,7 +30948,7 @@
         <v>1392</v>
       </c>
       <c r="C1401">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1401">
         <v>11</v>
@@ -31019,7 +31016,7 @@
         <v>1396</v>
       </c>
       <c r="C1405">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1405">
         <v>11</v>
@@ -31039,7 +31036,7 @@
         <v>14</v>
       </c>
       <c r="D1406">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1406">
         <v>2</v>
@@ -31070,7 +31067,7 @@
         <v>1399</v>
       </c>
       <c r="C1408">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1408">
         <v>12</v>
@@ -31107,7 +31104,7 @@
         <v>12</v>
       </c>
       <c r="D1410">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1410">
         <v>2</v>
@@ -31175,7 +31172,7 @@
         <v>12</v>
       </c>
       <c r="D1414">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1414">
         <v>2</v>
@@ -31206,7 +31203,7 @@
         <v>1407</v>
       </c>
       <c r="C1416">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D1416">
         <v>12</v>
@@ -31226,7 +31223,7 @@
         <v>15</v>
       </c>
       <c r="D1417">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1417">
         <v>2</v>
@@ -31257,7 +31254,7 @@
         <v>1410</v>
       </c>
       <c r="C1419">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1419">
         <v>11</v>
@@ -31294,7 +31291,7 @@
         <v>14</v>
       </c>
       <c r="D1421">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1421">
         <v>2</v>
@@ -31325,7 +31322,7 @@
         <v>1414</v>
       </c>
       <c r="C1423">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1423">
         <v>9</v>
@@ -31362,7 +31359,7 @@
         <v>16</v>
       </c>
       <c r="D1425">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1425">
         <v>2</v>
@@ -31393,7 +31390,7 @@
         <v>1418</v>
       </c>
       <c r="C1427">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1427">
         <v>11</v>
@@ -31413,7 +31410,7 @@
         <v>14</v>
       </c>
       <c r="D1428">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1428">
         <v>2</v>
@@ -31444,7 +31441,7 @@
         <v>1421</v>
       </c>
       <c r="C1430">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1430">
         <v>10</v>
@@ -31481,7 +31478,7 @@
         <v>13</v>
       </c>
       <c r="D1432">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1432">
         <v>2</v>
@@ -31512,7 +31509,7 @@
         <v>1425</v>
       </c>
       <c r="C1434">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1434">
         <v>11</v>
@@ -31532,7 +31529,7 @@
         <v>15</v>
       </c>
       <c r="D1435">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1435">
         <v>2</v>
@@ -31563,7 +31560,7 @@
         <v>1428</v>
       </c>
       <c r="C1437">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D1437">
         <v>13</v>
@@ -31600,7 +31597,7 @@
         <v>12</v>
       </c>
       <c r="D1439">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1439">
         <v>2</v>
@@ -31631,7 +31628,7 @@
         <v>1432</v>
       </c>
       <c r="C1441">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1441">
         <v>11</v>
@@ -31668,7 +31665,7 @@
         <v>13</v>
       </c>
       <c r="D1443">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1443">
         <v>2</v>
@@ -31699,7 +31696,7 @@
         <v>1436</v>
       </c>
       <c r="C1445">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1445">
         <v>12</v>
@@ -31750,7 +31747,7 @@
         <v>1439</v>
       </c>
       <c r="C1448">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1448">
         <v>12</v>
@@ -31787,7 +31784,7 @@
         <v>12</v>
       </c>
       <c r="D1450">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1450">
         <v>2</v>
@@ -31818,7 +31815,7 @@
         <v>1443</v>
       </c>
       <c r="C1452">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D1452">
         <v>9</v>
@@ -31855,7 +31852,7 @@
         <v>15</v>
       </c>
       <c r="D1454">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1454">
         <v>2</v>
@@ -31886,7 +31883,7 @@
         <v>1447</v>
       </c>
       <c r="C1456">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D1456">
         <v>11</v>
@@ -31937,7 +31934,7 @@
         <v>1450</v>
       </c>
       <c r="C1459">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1459">
         <v>11</v>
@@ -32005,7 +32002,7 @@
         <v>1454</v>
       </c>
       <c r="C1463">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1463">
         <v>11</v>
@@ -32042,7 +32039,7 @@
         <v>14</v>
       </c>
       <c r="D1465">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1465">
         <v>2</v>
@@ -32073,7 +32070,7 @@
         <v>1458</v>
       </c>
       <c r="C1467">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1467">
         <v>12</v>
@@ -32093,7 +32090,7 @@
         <v>13</v>
       </c>
       <c r="D1468">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1468">
         <v>2</v>
@@ -32348,7 +32345,7 @@
         <v>13</v>
       </c>
       <c r="D1483">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1483">
         <v>2</v>
@@ -32379,7 +32376,7 @@
         <v>1476</v>
       </c>
       <c r="C1485">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1485">
         <v>12</v>
@@ -32399,7 +32396,7 @@
         <v>12</v>
       </c>
       <c r="D1486">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1486">
         <v>2</v>
@@ -32430,7 +32427,7 @@
         <v>1479</v>
       </c>
       <c r="C1488">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1488">
         <v>10</v>
@@ -32467,7 +32464,7 @@
         <v>14</v>
       </c>
       <c r="D1490">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1490">
         <v>2</v>
@@ -32498,7 +32495,7 @@
         <v>1483</v>
       </c>
       <c r="C1492">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1492">
         <v>13</v>
@@ -32535,7 +32532,7 @@
         <v>13</v>
       </c>
       <c r="D1494">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1494">
         <v>2</v>
@@ -32566,7 +32563,7 @@
         <v>1487</v>
       </c>
       <c r="C1496">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D1496">
         <v>11</v>
@@ -32586,7 +32583,7 @@
         <v>17</v>
       </c>
       <c r="D1497">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1497">
         <v>2</v>
@@ -32617,7 +32614,7 @@
         <v>1490</v>
       </c>
       <c r="C1499">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D1499">
         <v>9</v>
@@ -32654,7 +32651,7 @@
         <v>14</v>
       </c>
       <c r="D1501">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1501">
         <v>2</v>
@@ -32685,7 +32682,7 @@
         <v>1494</v>
       </c>
       <c r="C1503">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1503">
         <v>11</v>
@@ -32722,7 +32719,7 @@
         <v>13</v>
       </c>
       <c r="D1505">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1505">
         <v>2</v>
@@ -32753,7 +32750,7 @@
         <v>1498</v>
       </c>
       <c r="C1507">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1507">
         <v>9</v>
@@ -32773,7 +32770,7 @@
         <v>12</v>
       </c>
       <c r="D1508">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1508">
         <v>2</v>
@@ -32804,7 +32801,7 @@
         <v>1501</v>
       </c>
       <c r="C1510">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1510">
         <v>11</v>
@@ -32841,7 +32838,7 @@
         <v>11</v>
       </c>
       <c r="D1512">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1512">
         <v>2</v>
@@ -32872,7 +32869,7 @@
         <v>1505</v>
       </c>
       <c r="C1514">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1514">
         <v>10</v>
@@ -32892,7 +32889,7 @@
         <v>13</v>
       </c>
       <c r="D1515">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1515">
         <v>2</v>
@@ -32923,7 +32920,7 @@
         <v>1508</v>
       </c>
       <c r="C1517">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1517">
         <v>12</v>
@@ -32960,7 +32957,7 @@
         <v>12</v>
       </c>
       <c r="D1519">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1519">
         <v>2</v>
@@ -32991,7 +32988,7 @@
         <v>1512</v>
       </c>
       <c r="C1521">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1521">
         <v>11</v>
@@ -33059,7 +33056,7 @@
         <v>1516</v>
       </c>
       <c r="C1525">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1525">
         <v>11</v>
@@ -33147,7 +33144,7 @@
         <v>12</v>
       </c>
       <c r="D1530">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1530">
         <v>2</v>
@@ -33178,7 +33175,7 @@
         <v>1523</v>
       </c>
       <c r="C1532">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1532">
         <v>10</v>
@@ -33215,7 +33212,7 @@
         <v>13</v>
       </c>
       <c r="D1534">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1534">
         <v>2</v>
@@ -33246,7 +33243,7 @@
         <v>1527</v>
       </c>
       <c r="C1536">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1536">
         <v>11</v>
@@ -33334,7 +33331,7 @@
         <v>12</v>
       </c>
       <c r="D1541">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1541">
         <v>2</v>
@@ -33385,7 +33382,7 @@
         <v>12</v>
       </c>
       <c r="D1544">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1544">
         <v>2</v>
@@ -33416,7 +33413,7 @@
         <v>1537</v>
       </c>
       <c r="C1546">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1546">
         <v>11</v>
@@ -33453,7 +33450,7 @@
         <v>11</v>
       </c>
       <c r="D1548">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1548">
         <v>2</v>
@@ -33484,7 +33481,7 @@
         <v>1541</v>
       </c>
       <c r="C1550">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1550">
         <v>10</v>
@@ -33521,7 +33518,7 @@
         <v>12</v>
       </c>
       <c r="D1552">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1552">
         <v>2</v>
@@ -33572,7 +33569,7 @@
         <v>12</v>
       </c>
       <c r="D1555">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1555">
         <v>2</v>
@@ -33671,7 +33668,7 @@
         <v>1552</v>
       </c>
       <c r="C1561">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1561">
         <v>10</v>
@@ -33708,7 +33705,7 @@
         <v>11</v>
       </c>
       <c r="D1563">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1563">
         <v>2</v>
@@ -33739,7 +33736,7 @@
         <v>1556</v>
       </c>
       <c r="C1565">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1565">
         <v>8</v>
@@ -33759,7 +33756,7 @@
         <v>10</v>
       </c>
       <c r="D1566">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1566">
         <v>2</v>
@@ -33790,7 +33787,7 @@
         <v>1559</v>
       </c>
       <c r="C1568">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D1568">
         <v>10</v>
@@ -33858,7 +33855,7 @@
         <v>1563</v>
       </c>
       <c r="C1572">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1572">
         <v>10</v>
@@ -33909,7 +33906,7 @@
         <v>1566</v>
       </c>
       <c r="C1575">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D1575">
         <v>10</v>
@@ -33946,7 +33943,7 @@
         <v>14</v>
       </c>
       <c r="D1577">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1577">
         <v>2</v>
@@ -33977,7 +33974,7 @@
         <v>1570</v>
       </c>
       <c r="C1579">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1579">
         <v>7</v>
@@ -34014,7 +34011,7 @@
         <v>11</v>
       </c>
       <c r="D1581">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1581">
         <v>2</v>
@@ -34045,7 +34042,7 @@
         <v>1574</v>
       </c>
       <c r="C1583">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1583">
         <v>10</v>
@@ -34133,7 +34130,7 @@
         <v>13</v>
       </c>
       <c r="D1588">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1588">
         <v>2</v>
@@ -34164,7 +34161,7 @@
         <v>1581</v>
       </c>
       <c r="C1590">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1590">
         <v>11</v>
@@ -34232,7 +34229,7 @@
         <v>1585</v>
       </c>
       <c r="C1594">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1594">
         <v>11</v>
@@ -34252,7 +34249,7 @@
         <v>11</v>
       </c>
       <c r="D1595">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1595">
         <v>2</v>
@@ -34283,7 +34280,7 @@
         <v>1588</v>
       </c>
       <c r="C1597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1597">
         <v>10</v>
@@ -34320,7 +34317,7 @@
         <v>12</v>
       </c>
       <c r="D1599">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1599">
         <v>2</v>
@@ -34351,7 +34348,7 @@
         <v>1592</v>
       </c>
       <c r="C1601">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1601">
         <v>9</v>
@@ -34371,7 +34368,7 @@
         <v>10</v>
       </c>
       <c r="D1602">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1602">
         <v>2</v>
@@ -34391,7 +34388,7 @@
         <v>8</v>
       </c>
       <c r="E1603">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1604" spans="1:5" x14ac:dyDescent="0.25">
@@ -34419,7 +34416,7 @@
         <v>1596</v>
       </c>
       <c r="C1605">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D1605">
         <v>8</v>
@@ -34439,7 +34436,7 @@
         <v>14</v>
       </c>
       <c r="D1606">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1606">
         <v>3</v>
@@ -34470,7 +34467,7 @@
         <v>1599</v>
       </c>
       <c r="C1608">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D1608">
         <v>14</v>
@@ -34507,7 +34504,7 @@
         <v>19</v>
       </c>
       <c r="D1610">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1610">
         <v>3</v>
@@ -34538,7 +34535,7 @@
         <v>1603</v>
       </c>
       <c r="C1612">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1612">
         <v>12</v>
@@ -34558,7 +34555,7 @@
         <v>21</v>
       </c>
       <c r="D1613">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1613">
         <v>3</v>
@@ -34606,7 +34603,7 @@
         <v>1607</v>
       </c>
       <c r="C1616">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D1616">
         <v>16</v>
@@ -34626,7 +34623,7 @@
         <v>25</v>
       </c>
       <c r="D1617">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1617">
         <v>3</v>
@@ -34657,7 +34654,7 @@
         <v>1610</v>
       </c>
       <c r="C1619">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D1619">
         <v>17</v>
@@ -34694,7 +34691,7 @@
         <v>28</v>
       </c>
       <c r="D1621">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1621">
         <v>3</v>
@@ -34725,7 +34722,7 @@
         <v>1614</v>
       </c>
       <c r="C1623">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1623">
         <v>20</v>
@@ -34745,7 +34742,7 @@
         <v>35</v>
       </c>
       <c r="D1624">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1624">
         <v>3</v>
@@ -34776,7 +34773,7 @@
         <v>1617</v>
       </c>
       <c r="C1626">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D1626">
         <v>21</v>
@@ -34813,7 +34810,7 @@
         <v>43</v>
       </c>
       <c r="D1628">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E1628">
         <v>3</v>
@@ -34844,7 +34841,7 @@
         <v>1621</v>
       </c>
       <c r="C1630">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D1630">
         <v>27</v>
@@ -34881,7 +34878,7 @@
         <v>47</v>
       </c>
       <c r="D1632">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1632">
         <v>3</v>
@@ -34912,7 +34909,7 @@
         <v>1625</v>
       </c>
       <c r="C1634">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D1634">
         <v>28</v>
@@ -34932,7 +34929,7 @@
         <v>52</v>
       </c>
       <c r="D1635">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E1635">
         <v>3</v>
@@ -34963,7 +34960,7 @@
         <v>1628</v>
       </c>
       <c r="C1637">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D1637">
         <v>32</v>
@@ -35000,7 +34997,7 @@
         <v>56</v>
       </c>
       <c r="D1639">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1639">
         <v>3</v>
@@ -35031,7 +35028,7 @@
         <v>1632</v>
       </c>
       <c r="C1641">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1641">
         <v>33</v>
@@ -35051,7 +35048,7 @@
         <v>59</v>
       </c>
       <c r="D1642">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E1642">
         <v>3</v>
@@ -35082,7 +35079,7 @@
         <v>1635</v>
       </c>
       <c r="C1644">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D1644">
         <v>36</v>
@@ -35119,7 +35116,7 @@
         <v>64</v>
       </c>
       <c r="D1646">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E1646">
         <v>3</v>
@@ -35150,7 +35147,7 @@
         <v>1639</v>
       </c>
       <c r="C1648">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1648">
         <v>41</v>
@@ -35187,7 +35184,7 @@
         <v>67</v>
       </c>
       <c r="D1650">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E1650">
         <v>3</v>
@@ -35218,7 +35215,7 @@
         <v>1643</v>
       </c>
       <c r="C1652">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1652">
         <v>45</v>
@@ -35255,7 +35252,7 @@
         <v>69</v>
       </c>
       <c r="D1654">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E1654">
         <v>3</v>
@@ -35269,7 +35266,7 @@
         <v>1646</v>
       </c>
       <c r="C1655">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1655">
         <v>49</v>
@@ -35306,7 +35303,7 @@
         <v>71</v>
       </c>
       <c r="D1657">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1657">
         <v>3</v>
@@ -35337,7 +35334,7 @@
         <v>1650</v>
       </c>
       <c r="C1659">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1659">
         <v>50</v>
@@ -35374,7 +35371,7 @@
         <v>72</v>
       </c>
       <c r="D1661">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1661">
         <v>3</v>
@@ -35405,7 +35402,7 @@
         <v>1654</v>
       </c>
       <c r="C1663">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1663">
         <v>52</v>
@@ -35425,7 +35422,7 @@
         <v>73</v>
       </c>
       <c r="D1664">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E1664">
         <v>3</v>
@@ -35456,7 +35453,7 @@
         <v>1657</v>
       </c>
       <c r="C1666">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1666">
         <v>56</v>
@@ -35493,7 +35490,7 @@
         <v>74</v>
       </c>
       <c r="D1668">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1668">
         <v>3</v>
@@ -35544,7 +35541,7 @@
         <v>74</v>
       </c>
       <c r="D1671">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1671">
         <v>3</v>
@@ -35592,7 +35589,7 @@
         <v>1665</v>
       </c>
       <c r="C1674">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1674">
         <v>61</v>
@@ -35612,7 +35609,7 @@
         <v>75</v>
       </c>
       <c r="D1675">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E1675">
         <v>3</v>
@@ -35680,7 +35677,7 @@
         <v>75</v>
       </c>
       <c r="D1679">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1679">
         <v>3</v>
@@ -35731,7 +35728,7 @@
         <v>75</v>
       </c>
       <c r="D1682">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1682">
         <v>3</v>
@@ -35762,7 +35759,7 @@
         <v>1675</v>
       </c>
       <c r="C1684">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1684">
         <v>66</v>
@@ -35799,7 +35796,7 @@
         <v>76</v>
       </c>
       <c r="D1686">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1686">
         <v>3</v>
@@ -35830,7 +35827,7 @@
         <v>1679</v>
       </c>
       <c r="C1688">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1688">
         <v>68</v>
@@ -35867,7 +35864,7 @@
         <v>75</v>
       </c>
       <c r="D1690">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1690">
         <v>3</v>
@@ -35898,7 +35895,7 @@
         <v>1683</v>
       </c>
       <c r="C1692">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1692">
         <v>69</v>
@@ -35918,7 +35915,7 @@
         <v>76</v>
       </c>
       <c r="D1693">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1693">
         <v>3</v>
@@ -35949,7 +35946,7 @@
         <v>1686</v>
       </c>
       <c r="C1695">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1695">
         <v>71</v>
@@ -35986,7 +35983,7 @@
         <v>77</v>
       </c>
       <c r="D1697">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1697">
         <v>3</v>
@@ -36105,7 +36102,7 @@
         <v>77</v>
       </c>
       <c r="D1704">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1704">
         <v>3</v>
@@ -36224,7 +36221,7 @@
         <v>77</v>
       </c>
       <c r="D1711">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1711">
         <v>3</v>
@@ -36360,7 +36357,7 @@
         <v>77</v>
       </c>
       <c r="D1719">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1719">
         <v>3</v>
@@ -36391,7 +36388,7 @@
         <v>1712</v>
       </c>
       <c r="C1721">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1721">
         <v>75</v>
@@ -36442,7 +36439,7 @@
         <v>1715</v>
       </c>
       <c r="C1724">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1724">
         <v>75</v>
@@ -36510,7 +36507,7 @@
         <v>1719</v>
       </c>
       <c r="C1728">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1728">
         <v>75</v>
@@ -36547,7 +36544,7 @@
         <v>78</v>
       </c>
       <c r="D1730">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1730">
         <v>3</v>
@@ -36666,7 +36663,7 @@
         <v>78</v>
       </c>
       <c r="D1737">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1737">
         <v>3</v>
@@ -36697,7 +36694,7 @@
         <v>1730</v>
       </c>
       <c r="C1739">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1739">
         <v>77</v>
@@ -36765,7 +36762,7 @@
         <v>1734</v>
       </c>
       <c r="C1743">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1743">
         <v>77</v>
@@ -36802,7 +36799,7 @@
         <v>78</v>
       </c>
       <c r="D1745">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1745">
         <v>3</v>
@@ -36816,7 +36813,7 @@
         <v>1737</v>
       </c>
       <c r="C1746">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1746">
         <v>78</v>
@@ -37040,7 +37037,7 @@
         <v>77</v>
       </c>
       <c r="D1759">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E1759">
         <v>3</v>
@@ -37122,7 +37119,7 @@
         <v>1755</v>
       </c>
       <c r="C1764">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1764">
         <v>79</v>
@@ -37190,7 +37187,7 @@
         <v>1759</v>
       </c>
       <c r="C1768">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1768">
         <v>79</v>
@@ -37278,7 +37275,7 @@
         <v>77</v>
       </c>
       <c r="D1773">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E1773">
         <v>3</v>
@@ -37377,7 +37374,7 @@
         <v>1770</v>
       </c>
       <c r="C1779">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1779">
         <v>80</v>
@@ -37428,7 +37425,7 @@
         <v>1773</v>
       </c>
       <c r="C1782">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1782">
         <v>80</v>
@@ -37652,7 +37649,7 @@
         <v>77</v>
       </c>
       <c r="D1795">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1795">
         <v>3</v>
@@ -38077,7 +38074,7 @@
         <v>77</v>
       </c>
       <c r="D1820">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E1820">
         <v>3</v>
@@ -38176,7 +38173,7 @@
         <v>1817</v>
       </c>
       <c r="C1826">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1826">
         <v>82</v>
@@ -38244,7 +38241,7 @@
         <v>1821</v>
       </c>
       <c r="C1830">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1830">
         <v>82</v>
@@ -38295,7 +38292,7 @@
         <v>1824</v>
       </c>
       <c r="C1833">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1833">
         <v>82</v>
@@ -38312,7 +38309,7 @@
         <v>1825</v>
       </c>
       <c r="C1834">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D1834">
         <v>82</v>
@@ -38363,7 +38360,7 @@
         <v>1828</v>
       </c>
       <c r="C1837">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D1837">
         <v>82</v>
@@ -38400,7 +38397,7 @@
         <v>77</v>
       </c>
       <c r="D1839">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1839">
         <v>3</v>
@@ -38451,7 +38448,7 @@
         <v>77</v>
       </c>
       <c r="D1842">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1842">
         <v>3</v>
@@ -38482,7 +38479,7 @@
         <v>1835</v>
       </c>
       <c r="C1844">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D1844">
         <v>82</v>
@@ -38519,7 +38516,7 @@
         <v>100</v>
       </c>
       <c r="D1846">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1846">
         <v>3</v>
@@ -38550,7 +38547,7 @@
         <v>1839</v>
       </c>
       <c r="C1848">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D1848">
         <v>83</v>
@@ -38706,7 +38703,7 @@
         <v>77</v>
       </c>
       <c r="D1857">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1857">
         <v>3</v>
@@ -38737,7 +38734,7 @@
         <v>1850</v>
       </c>
       <c r="C1859">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D1859">
         <v>82</v>
@@ -38788,7 +38785,7 @@
         <v>1853</v>
       </c>
       <c r="C1862">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D1862">
         <v>82</v>
@@ -38944,7 +38941,7 @@
         <v>77</v>
       </c>
       <c r="D1871">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1871">
         <v>3</v>
@@ -38975,7 +38972,7 @@
         <v>1864</v>
       </c>
       <c r="C1873">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1873">
         <v>83</v>
@@ -39043,7 +39040,7 @@
         <v>1868</v>
       </c>
       <c r="C1877">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1877">
         <v>83</v>
@@ -39094,7 +39091,7 @@
         <v>1871</v>
       </c>
       <c r="C1880">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1880">
         <v>83</v>
@@ -39162,7 +39159,7 @@
         <v>1875</v>
       </c>
       <c r="C1884">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1884">
         <v>83</v>
@@ -39281,7 +39278,7 @@
         <v>1882</v>
       </c>
       <c r="C1891">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1891">
         <v>83</v>
@@ -39468,7 +39465,7 @@
         <v>1893</v>
       </c>
       <c r="C1902">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1902">
         <v>83</v>
@@ -39536,7 +39533,7 @@
         <v>1897</v>
       </c>
       <c r="C1906">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1906">
         <v>83</v>
@@ -39604,7 +39601,7 @@
         <v>1901</v>
       </c>
       <c r="C1910">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1910">
         <v>83</v>
@@ -39842,7 +39839,7 @@
         <v>1915</v>
       </c>
       <c r="C1924">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1924">
         <v>83</v>
@@ -39910,7 +39907,7 @@
         <v>1919</v>
       </c>
       <c r="C1928">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1928">
         <v>83</v>
@@ -40117,7 +40114,7 @@
         <v>75</v>
       </c>
       <c r="D1940">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E1940">
         <v>3</v>
@@ -40423,7 +40420,7 @@
         <v>75</v>
       </c>
       <c r="D1958">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E1958">
         <v>3</v>
@@ -40491,7 +40488,7 @@
         <v>75</v>
       </c>
       <c r="D1962">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E1962">
         <v>3</v>
@@ -40709,7 +40706,7 @@
         <v>1966</v>
       </c>
       <c r="C1975">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1975">
         <v>84</v>
@@ -40777,7 +40774,7 @@
         <v>1970</v>
       </c>
       <c r="C1979">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1979">
         <v>84</v>
@@ -41202,7 +41199,7 @@
         <v>1995</v>
       </c>
       <c r="C2004">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2004">
         <v>84</v>
@@ -41321,7 +41318,7 @@
         <v>2002</v>
       </c>
       <c r="C2011">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2011">
         <v>84</v>
@@ -41763,7 +41760,7 @@
         <v>2028</v>
       </c>
       <c r="C2037">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2037">
         <v>84</v>
@@ -41814,7 +41811,7 @@
         <v>2031</v>
       </c>
       <c r="C2040">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2040">
         <v>84</v>
@@ -41902,7 +41899,7 @@
         <v>75</v>
       </c>
       <c r="D2045">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2045">
         <v>3</v>
@@ -42120,7 +42117,7 @@
         <v>2049</v>
       </c>
       <c r="C2058">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2058">
         <v>85</v>
@@ -42225,7 +42222,7 @@
         <v>74</v>
       </c>
       <c r="D2064">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2064">
         <v>3</v>
@@ -42256,7 +42253,7 @@
         <v>2057</v>
       </c>
       <c r="C2066">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2066">
         <v>84</v>
@@ -42307,7 +42304,7 @@
         <v>2060</v>
       </c>
       <c r="C2069">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2069">
         <v>84</v>
@@ -42375,7 +42372,7 @@
         <v>2064</v>
       </c>
       <c r="C2073">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2073">
         <v>84</v>
@@ -42443,7 +42440,7 @@
         <v>2068</v>
       </c>
       <c r="C2077">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2077">
         <v>84</v>
@@ -42531,7 +42528,7 @@
         <v>74</v>
       </c>
       <c r="D2082">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2082">
         <v>3</v>
@@ -42582,7 +42579,7 @@
         <v>74</v>
       </c>
       <c r="D2085">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2085">
         <v>3</v>
@@ -42650,7 +42647,7 @@
         <v>74</v>
       </c>
       <c r="D2089">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2089">
         <v>3</v>
@@ -42718,7 +42715,7 @@
         <v>74</v>
       </c>
       <c r="D2093">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2093">
         <v>3</v>
@@ -42868,7 +42865,7 @@
         <v>2093</v>
       </c>
       <c r="C2102">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2102">
         <v>84</v>
@@ -42956,7 +42953,7 @@
         <v>75</v>
       </c>
       <c r="D2107">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2107">
         <v>3</v>
@@ -42987,7 +42984,7 @@
         <v>2100</v>
       </c>
       <c r="C2109">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2109">
         <v>85</v>
@@ -43143,7 +43140,7 @@
         <v>74</v>
       </c>
       <c r="D2118">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2118">
         <v>3</v>
@@ -43242,7 +43239,7 @@
         <v>2115</v>
       </c>
       <c r="C2124">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2124">
         <v>84</v>
@@ -43293,7 +43290,7 @@
         <v>2118</v>
       </c>
       <c r="C2127">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2127">
         <v>84</v>
@@ -43361,7 +43358,7 @@
         <v>2122</v>
       </c>
       <c r="C2131">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2131">
         <v>84</v>
@@ -43398,7 +43395,7 @@
         <v>75</v>
       </c>
       <c r="D2133">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2133">
         <v>3</v>
@@ -43429,7 +43426,7 @@
         <v>2126</v>
       </c>
       <c r="C2135">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2135">
         <v>85</v>
@@ -43480,7 +43477,7 @@
         <v>2129</v>
       </c>
       <c r="C2138">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2138">
         <v>85</v>
@@ -43548,7 +43545,7 @@
         <v>2133</v>
       </c>
       <c r="C2142">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2142">
         <v>85</v>
@@ -43568,7 +43565,7 @@
         <v>74</v>
       </c>
       <c r="D2143">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2143">
         <v>3</v>
@@ -43667,7 +43664,7 @@
         <v>2140</v>
       </c>
       <c r="C2149">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2149">
         <v>84</v>
@@ -43735,7 +43732,7 @@
         <v>2144</v>
       </c>
       <c r="C2153">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2153">
         <v>84</v>
@@ -43755,7 +43752,7 @@
         <v>74</v>
       </c>
       <c r="D2154">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2154">
         <v>3</v>
@@ -43823,7 +43820,7 @@
         <v>74</v>
       </c>
       <c r="D2158">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2158">
         <v>3</v>
@@ -43868,7 +43865,7 @@
         <v>45694</v>
       </c>
       <c r="B2161" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C2161">
         <v>74</v>
@@ -43973,7 +43970,7 @@
         <v>2157</v>
       </c>
       <c r="C2167">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2167">
         <v>84</v>
@@ -44024,7 +44021,7 @@
         <v>2160</v>
       </c>
       <c r="C2170">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2170">
         <v>84</v>
@@ -44092,7 +44089,7 @@
         <v>2164</v>
       </c>
       <c r="C2174">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2174">
         <v>84</v>
@@ -44330,7 +44327,7 @@
         <v>2178</v>
       </c>
       <c r="C2188">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2188">
         <v>84</v>
@@ -44398,7 +44395,7 @@
         <v>2182</v>
       </c>
       <c r="C2192">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2192">
         <v>84</v>
@@ -44466,7 +44463,7 @@
         <v>2186</v>
       </c>
       <c r="C2196">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2196">
         <v>84</v>
@@ -44517,7 +44514,7 @@
         <v>2189</v>
       </c>
       <c r="C2199">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2199">
         <v>84</v>
@@ -44554,7 +44551,7 @@
         <v>73</v>
       </c>
       <c r="D2201">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2201">
         <v>3</v>
@@ -44653,7 +44650,7 @@
         <v>2197</v>
       </c>
       <c r="C2207">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2207">
         <v>85</v>
@@ -44679,66 +44676,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2209" s="1">
-        <v>45694</v>
-      </c>
-      <c r="B2209" t="s">
-        <v>2199</v>
-      </c>
-      <c r="C2209">
-        <v>74</v>
-      </c>
-      <c r="D2209">
-        <v>85</v>
-      </c>
-      <c r="E2209">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2209" s="1"/>
+    </row>
+    <row r="2210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2210" s="1"/>
     </row>
-    <row r="2211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2211" s="1"/>
     </row>
-    <row r="2212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2212" s="1"/>
     </row>
-    <row r="2213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2213" s="1"/>
     </row>
-    <row r="2214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2214" s="1"/>
     </row>
-    <row r="2215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2215" s="1"/>
     </row>
-    <row r="2216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2216" s="1"/>
     </row>
-    <row r="2217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2217" s="1"/>
     </row>
-    <row r="2218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2218" s="1"/>
     </row>
-    <row r="2219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2219" s="1"/>
     </row>
-    <row r="2220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2220" s="1"/>
     </row>
-    <row r="2221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2221" s="1"/>
     </row>
-    <row r="2222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2222" s="1"/>
     </row>
-    <row r="2223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2223" s="1"/>
     </row>
-    <row r="2224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2224" s="1"/>
     </row>
     <row r="2225" spans="1:1" x14ac:dyDescent="0.25">
@@ -45241,9 +45224,6 @@
     </row>
     <row r="2391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2391" s="1"/>
-    </row>
-    <row r="2392" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2392" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
